--- a/Sistema_Inventario_NEMET_Final.xlsx
+++ b/Sistema_Inventario_NEMET_Final.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventario" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cotizador_Rendimientos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cat_Productos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Inventario" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Cotizador_Rendimientos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Cat_Productos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Clientes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5191,7 +5192,6 @@
           <t>Producto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
       <c r="C1" t="inlineStr">
         <is>
           <t>Presentacion</t>
@@ -6185,6 +6185,66 @@
       <c r="G45" t="n">
         <v>0</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Correo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Teléfono</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Dirección</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Luis Manuel Merelles Lourido</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nemet</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>luismerelles@gmail.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Sistema_Inventario_NEMET_Final.xlsx
+++ b/Sistema_Inventario_NEMET_Final.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Cotizador_Rendimientos" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Cat_Productos" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Clientes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Historial_Cotizaciones" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6243,8 +6244,72 @@
           <t>luismerelles@gmail.com</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Folio</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Detalle_Productos</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>COT-2026-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:49:26</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Cliente General</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>13x EPO-DEEP TRANSPARENTE (1.420 kg) [16.00 m² x 1 mm]</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>10010</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Sistema_Inventario_NEMET_Final.xlsx
+++ b/Sistema_Inventario_NEMET_Final.xlsx
@@ -6256,7 +6256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6311,6 +6311,31 @@
         <v>10010</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>COT-2026-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:58:48</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Luis Manuel Merelles Lourido</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2x EPO-DEEP TRANSPARENTE (7.100 kg) [12.00 m² x 1 mm]</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>7110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Sistema_Inventario_NEMET_Final.xlsx
+++ b/Sistema_Inventario_NEMET_Final.xlsx
@@ -6256,7 +6256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6294,45 +6294,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28 12:49:26</t>
+          <t>2026-09-28 14:10:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cliente General</t>
+          <t>Luis Manuel Merelles Lourido</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13x EPO-DEEP TRANSPARENTE (1.420 kg) [16.00 m² x 1 mm]</t>
+          <t>2x EPO-DEEP TRANSPARENTE (7.100 kg) [12.00 m² x 1 mm]</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>COT-2026-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-28 13:58:48</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Luis Manuel Merelles Lourido</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2x EPO-DEEP TRANSPARENTE (7.100 kg) [12.00 m² x 1 mm]</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
         <v>7110</v>
       </c>
     </row>

--- a/Sistema_Inventario_NEMET_Final.xlsx
+++ b/Sistema_Inventario_NEMET_Final.xlsx
@@ -3539,7 +3539,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EM 01</t>
+          <t>EMI 01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3594,7 +3594,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EM 02</t>
+          <t>EMI 02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3759,7 +3759,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EP 01</t>
+          <t>EPA 01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">

--- a/Sistema_Inventario_NEMET_Final.xlsx
+++ b/Sistema_Inventario_NEMET_Final.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:Q90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>655.87</v>
       </c>
       <c r="K3" t="n">
-        <v>663.7931034482759</v>
+        <v>685.344827586207</v>
       </c>
       <c r="L3" t="n">
-        <v>106.2068965517242</v>
+        <v>109.655172413793</v>
       </c>
       <c r="M3" t="n">
-        <v>770.0000000000001</v>
+        <v>795</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>663.7931034482759</v>
+        <v>685.344827586207</v>
       </c>
     </row>
     <row r="4">
@@ -603,22 +603,22 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1967.61</v>
       </c>
       <c r="K4" t="n">
-        <v>1896.551724137931</v>
+        <v>2056.896551724138</v>
       </c>
       <c r="L4" t="n">
-        <v>303.448275862069</v>
+        <v>329.1034482758619</v>
       </c>
       <c r="M4" t="n">
-        <v>2200</v>
+        <v>2386</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1896.551724137931</v>
+        <v>2056.896551724138</v>
       </c>
     </row>
     <row r="5">
@@ -658,22 +658,22 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3015.44</v>
       </c>
       <c r="K5" t="n">
-        <v>3064.655172413793</v>
+        <v>3182.758620689655</v>
       </c>
       <c r="L5" t="n">
-        <v>490.3448275862069</v>
+        <v>509.2413793103447</v>
       </c>
       <c r="M5" t="n">
-        <v>3555</v>
+        <v>3692</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3064.655172413793</v>
+        <v>3182.758620689655</v>
       </c>
     </row>
     <row r="6">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>6635.89</v>
       </c>
       <c r="K6" t="n">
-        <v>7107.758620689656</v>
+        <v>7344.827586206897</v>
       </c>
       <c r="L6" t="n">
-        <v>1137.241379310345</v>
+        <v>1175.172413793103</v>
       </c>
       <c r="M6" t="n">
-        <v>8245</v>
+        <v>8520</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>7107.758620689656</v>
+        <v>7344.827586206897</v>
       </c>
     </row>
     <row r="7">
@@ -768,22 +768,22 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>784.48</v>
       </c>
       <c r="K7" t="n">
-        <v>818.9655172413794</v>
+        <v>827.5862068965517</v>
       </c>
       <c r="L7" t="n">
-        <v>131.0344827586207</v>
+        <v>132.4137931034483</v>
       </c>
       <c r="M7" t="n">
-        <v>950.0000000000001</v>
+        <v>960</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>818.9655172413794</v>
+        <v>827.5862068965517</v>
       </c>
     </row>
     <row r="8">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2241.3</v>
       </c>
       <c r="K8" t="n">
-        <v>2331.896551724138</v>
+        <v>2379.310344827587</v>
       </c>
       <c r="L8" t="n">
-        <v>373.1034482758621</v>
+        <v>380.6896551724135</v>
       </c>
       <c r="M8" t="n">
-        <v>2705</v>
+        <v>2760</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2331.896551724138</v>
+        <v>2379.310344827587</v>
       </c>
     </row>
     <row r="9">
@@ -878,22 +878,22 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>3557.7</v>
       </c>
       <c r="K9" t="n">
-        <v>3693.96551724138</v>
+        <v>3793.103448275862</v>
       </c>
       <c r="L9" t="n">
-        <v>591.0344827586208</v>
+        <v>606.8965517241377</v>
       </c>
       <c r="M9" t="n">
-        <v>4285.000000000001</v>
+        <v>4400</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3693.96551724138</v>
+        <v>3793.103448275862</v>
       </c>
     </row>
     <row r="10">
@@ -933,22 +933,22 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>6186.02</v>
       </c>
       <c r="K10" t="n">
-        <v>6668.103448275862</v>
+        <v>6879.310344827587</v>
       </c>
       <c r="L10" t="n">
-        <v>1066.896551724138</v>
+        <v>1100.689655172413</v>
       </c>
       <c r="M10" t="n">
-        <v>7735</v>
+        <v>7980</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>6668.103448275862</v>
+        <v>6879.310344827587</v>
       </c>
     </row>
     <row r="11">
@@ -988,22 +988,22 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>542.13</v>
       </c>
       <c r="K11" t="n">
-        <v>599.1379310344828</v>
+        <v>620.6896551724138</v>
       </c>
       <c r="L11" t="n">
-        <v>95.86206896551725</v>
+        <v>99.31034482758616</v>
       </c>
       <c r="M11" t="n">
-        <v>695</v>
+        <v>720</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>599.1379310344828</v>
+        <v>620.6896551724138</v>
       </c>
     </row>
     <row r="12">
@@ -1043,22 +1043,22 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1084.26</v>
       </c>
       <c r="K12" t="n">
-        <v>1133.620689655173</v>
+        <v>1241.379310344828</v>
       </c>
       <c r="L12" t="n">
-        <v>181.3793103448277</v>
+        <v>198.6206896551723</v>
       </c>
       <c r="M12" t="n">
-        <v>1315.000000000001</v>
+        <v>1440</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1133.620689655173</v>
+        <v>1241.379310344828</v>
       </c>
     </row>
     <row r="13">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2076.12</v>
       </c>
       <c r="K13" t="n">
-        <v>2172.413793103448</v>
+        <v>2379.310344827587</v>
       </c>
       <c r="L13" t="n">
-        <v>347.5862068965517</v>
+        <v>380.6896551724135</v>
       </c>
       <c r="M13" t="n">
-        <v>2520</v>
+        <v>2760</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2172.413793103448</v>
+        <v>2379.310344827587</v>
       </c>
     </row>
     <row r="14">
@@ -1153,22 +1153,22 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>3329.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3482.758620689655</v>
+        <v>3793.103448275862</v>
       </c>
       <c r="L14" t="n">
-        <v>557.2413793103448</v>
+        <v>606.8965517241377</v>
       </c>
       <c r="M14" t="n">
-        <v>4040</v>
+        <v>4400</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3482.758620689655</v>
+        <v>3793.103448275862</v>
       </c>
     </row>
     <row r="15">
@@ -1208,22 +1208,22 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>4752</v>
       </c>
       <c r="K15" t="n">
-        <v>5030.172413793104</v>
+        <v>5431.034482758621</v>
       </c>
       <c r="L15" t="n">
-        <v>804.8275862068967</v>
+        <v>868.9655172413786</v>
       </c>
       <c r="M15" t="n">
-        <v>5835.000000000001</v>
+        <v>6300</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5030.172413793104</v>
+        <v>5431.034482758621</v>
       </c>
     </row>
     <row r="16">
@@ -1263,22 +1263,22 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>6029</v>
       </c>
       <c r="K16" t="n">
-        <v>6456.896551724139</v>
+        <v>6896.551724137931</v>
       </c>
       <c r="L16" t="n">
-        <v>1033.103448275862</v>
+        <v>1103.448275862069</v>
       </c>
       <c r="M16" t="n">
-        <v>7490.000000000001</v>
+        <v>8000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>6456.896551724139</v>
+        <v>6896.551724137931</v>
       </c>
     </row>
     <row r="17">
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>537.29</v>
       </c>
       <c r="K17" t="n">
         <v>465.5172413793103</v>
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2927</v>
       </c>
       <c r="K18" t="n">
-        <v>3051.724137931035</v>
+        <v>3275.862068965518</v>
       </c>
       <c r="L18" t="n">
-        <v>488.2758620689656</v>
+        <v>524.1379310344823</v>
       </c>
       <c r="M18" t="n">
-        <v>3540</v>
+        <v>3800</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3051.724137931035</v>
+        <v>3275.862068965518</v>
       </c>
     </row>
     <row r="19">
@@ -1428,22 +1428,22 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>5533.91</v>
       </c>
       <c r="K19" t="n">
-        <v>5793.103448275862</v>
+        <v>6387.068965517242</v>
       </c>
       <c r="L19" t="n">
-        <v>926.896551724138</v>
+        <v>1021.931034482758</v>
       </c>
       <c r="M19" t="n">
-        <v>6720</v>
+        <v>7409</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5793.103448275862</v>
+        <v>6387.068965517242</v>
       </c>
     </row>
     <row r="20">
@@ -1483,22 +1483,22 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>522.86</v>
       </c>
       <c r="K20" t="n">
-        <v>530.1724137931035</v>
+        <v>551.7241379310345</v>
       </c>
       <c r="L20" t="n">
-        <v>84.82758620689656</v>
+        <v>88.27586206896547</v>
       </c>
       <c r="M20" t="n">
-        <v>615</v>
+        <v>640</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>530.1724137931035</v>
+        <v>551.7241379310345</v>
       </c>
     </row>
     <row r="21">
@@ -1538,22 +1538,22 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2608.4</v>
       </c>
       <c r="K21" t="n">
-        <v>2525.862068965517</v>
+        <v>2751.724137931035</v>
       </c>
       <c r="L21" t="n">
-        <v>404.1379310344828</v>
+        <v>440.2758620689651</v>
       </c>
       <c r="M21" t="n">
-        <v>2930</v>
+        <v>3192</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2525.862068965517</v>
+        <v>2751.724137931035</v>
       </c>
     </row>
     <row r="22">
@@ -1593,22 +1593,22 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>4731.74</v>
       </c>
       <c r="K22" t="n">
-        <v>4814.655172413793</v>
+        <v>5044.827586206897</v>
       </c>
       <c r="L22" t="n">
-        <v>770.3448275862069</v>
+        <v>807.1724137931033</v>
       </c>
       <c r="M22" t="n">
-        <v>5584.999999999999</v>
+        <v>5852</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4814.655172413793</v>
+        <v>5044.827586206897</v>
       </c>
     </row>
     <row r="23">
@@ -1648,22 +1648,22 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>7813.92</v>
       </c>
       <c r="K23" t="n">
-        <v>8275.862068965518</v>
+        <v>8689.655172413793</v>
       </c>
       <c r="L23" t="n">
-        <v>1324.137931034483</v>
+        <v>1390.344827586207</v>
       </c>
       <c r="M23" t="n">
-        <v>9600.000000000002</v>
+        <v>10080</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8275.862068965518</v>
+        <v>8689.655172413793</v>
       </c>
     </row>
     <row r="24">
@@ -1929,10 +1929,10 @@
         <v>64.65517241379311</v>
       </c>
       <c r="L28" t="n">
-        <v>10.3448275862069</v>
+        <v>10.34482758620689</v>
       </c>
       <c r="M28" t="n">
-        <v>75.00000000000001</v>
+        <v>75</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -1981,19 +1981,19 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>99.13793103448276</v>
+        <v>96.55172413793105</v>
       </c>
       <c r="L29" t="n">
-        <v>15.86206896551724</v>
+        <v>15.44827586206895</v>
       </c>
       <c r="M29" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>99.13793103448276</v>
+        <v>96.55172413793105</v>
       </c>
     </row>
     <row r="30">
@@ -2036,19 +2036,19 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>237.0689655172414</v>
+        <v>232.7586206896552</v>
       </c>
       <c r="L30" t="n">
-        <v>37.93103448275863</v>
+        <v>37.24137931034483</v>
       </c>
       <c r="M30" t="n">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>237.0689655172414</v>
+        <v>232.7586206896552</v>
       </c>
     </row>
     <row r="31">
@@ -2091,19 +2091,19 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>456.896551724138</v>
+        <v>448.2758620689655</v>
       </c>
       <c r="L31" t="n">
-        <v>73.10344827586208</v>
+        <v>71.72413793103448</v>
       </c>
       <c r="M31" t="n">
-        <v>530.0000000000001</v>
+        <v>520</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>456.896551724138</v>
+        <v>448.2758620689655</v>
       </c>
     </row>
     <row r="32">
@@ -2146,19 +2146,19 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>732.7586206896552</v>
+        <v>724.1379310344828</v>
       </c>
       <c r="L32" t="n">
-        <v>117.2413793103448</v>
+        <v>115.8620689655172</v>
       </c>
       <c r="M32" t="n">
-        <v>850.0000000000001</v>
+        <v>840</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>732.7586206896552</v>
+        <v>724.1379310344828</v>
       </c>
     </row>
     <row r="33">
@@ -2198,22 +2198,22 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>19.55</v>
       </c>
       <c r="K33" t="n">
-        <v>17.24137931034483</v>
+        <v>21.55172413793104</v>
       </c>
       <c r="L33" t="n">
-        <v>2.758620689655173</v>
+        <v>3.448275862068964</v>
       </c>
       <c r="M33" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>17.24137931034483</v>
+        <v>21.55172413793104</v>
       </c>
     </row>
     <row r="34">
@@ -2253,22 +2253,22 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>53.77</v>
       </c>
       <c r="K34" t="n">
-        <v>51.72413793103448</v>
+        <v>56.03448275862069</v>
       </c>
       <c r="L34" t="n">
-        <v>8.275862068965516</v>
+        <v>8.96551724137931</v>
       </c>
       <c r="M34" t="n">
-        <v>59.99999999999999</v>
+        <v>65</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>51.72413793103448</v>
+        <v>56.03448275862069</v>
       </c>
     </row>
     <row r="35">
@@ -2308,22 +2308,22 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>91.91</v>
       </c>
       <c r="K35" t="n">
-        <v>86.20689655172414</v>
+        <v>94.82758620689656</v>
       </c>
       <c r="L35" t="n">
-        <v>13.79310344827586</v>
+        <v>15.17241379310344</v>
       </c>
       <c r="M35" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>86.20689655172414</v>
+        <v>94.82758620689656</v>
       </c>
     </row>
     <row r="36">
@@ -2363,22 +2363,22 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>161.33</v>
       </c>
       <c r="K36" t="n">
-        <v>155.1724137931035</v>
+        <v>163.7931034482759</v>
       </c>
       <c r="L36" t="n">
-        <v>24.82758620689656</v>
+        <v>26.20689655172413</v>
       </c>
       <c r="M36" t="n">
-        <v>180.0000000000001</v>
+        <v>190</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>155.1724137931035</v>
+        <v>163.7931034482759</v>
       </c>
     </row>
     <row r="37">
@@ -2418,22 +2418,22 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>248.12</v>
       </c>
       <c r="K37" t="n">
-        <v>271.551724137931</v>
+        <v>275.8620689655173</v>
       </c>
       <c r="L37" t="n">
-        <v>43.44827586206896</v>
+        <v>44.13793103448273</v>
       </c>
       <c r="M37" t="n">
-        <v>314.9999999999999</v>
+        <v>320</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>271.551724137931</v>
+        <v>275.8620689655173</v>
       </c>
     </row>
     <row r="38">
@@ -2473,13 +2473,13 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>427.79</v>
       </c>
       <c r="K38" t="n">
         <v>474.1379310344828</v>
       </c>
       <c r="L38" t="n">
-        <v>75.86206896551725</v>
+        <v>75.86206896551721</v>
       </c>
       <c r="M38" t="n">
         <v>550</v>
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>421.06</v>
       </c>
       <c r="K47" t="n">
         <v>431.0344827586207</v>
       </c>
       <c r="L47" t="n">
-        <v>68.96551724137932</v>
+        <v>68.9655172413793</v>
       </c>
       <c r="M47" t="n">
         <v>500</v>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>&lt; 10 kg</t>
+          <t>0 a 59.999 kg</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -3023,22 +3023,22 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>182.7</v>
       </c>
       <c r="K48" t="n">
-        <v>172.4137931034483</v>
+        <v>176.7241379310345</v>
       </c>
       <c r="L48" t="n">
-        <v>27.58620689655173</v>
+        <v>28.27586206896549</v>
       </c>
       <c r="M48" t="n">
-        <v>200.0000000000001</v>
+        <v>205</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>172.4137931034483</v>
+        <v>176.7241379310345</v>
       </c>
     </row>
     <row r="49">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>10 a 20 kg</t>
+          <t>+ 60 kg</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -3078,38 +3078,38 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>182.7</v>
       </c>
       <c r="K49" t="n">
-        <v>168.1034482758621</v>
+        <v>172.4137931034483</v>
       </c>
       <c r="L49" t="n">
-        <v>26.89655172413794</v>
+        <v>27.58620689655172</v>
       </c>
       <c r="M49" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>168.1034482758621</v>
+        <v>172.4137931034483</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EH 03</t>
+          <t>EHC 01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EPOXY-HOJUELA (1 color)</t>
+          <t xml:space="preserve">EPOXY-HOJUELA (combinación) </t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>25 a 175 kg</t>
+          <t>0 a 59.999 kg</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -3133,28 +3133,28 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>214.5</v>
       </c>
       <c r="K50" t="n">
-        <v>159.4827586206897</v>
+        <v>202.5862068965517</v>
       </c>
       <c r="L50" t="n">
-        <v>25.51724137931035</v>
+        <v>32.41379310344826</v>
       </c>
       <c r="M50" t="n">
-        <v>185.0000000000001</v>
+        <v>235</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>159.4827586206897</v>
+        <v>202.5862068965517</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EHC 01</t>
+          <t>EHC 02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>&lt; 10 kg</t>
+          <t>+ 60 kg</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -3188,38 +3188,38 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>214.5</v>
       </c>
       <c r="K51" t="n">
-        <v>181.0344827586207</v>
+        <v>198.2758620689655</v>
       </c>
       <c r="L51" t="n">
-        <v>28.96551724137931</v>
+        <v>31.72413793103448</v>
       </c>
       <c r="M51" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>181.0344827586207</v>
+        <v>198.2758620689655</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EHC 02</t>
+          <t>EG 01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">EPOXY-HOJUELA (combinación) </t>
+          <t>EPOXY-GRANO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>10 a 20 kg</t>
+          <t>1 a 20 kg</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -3246,35 +3246,35 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>176.7241379310345</v>
+        <v>56.03448275862069</v>
       </c>
       <c r="L52" t="n">
-        <v>28.27586206896552</v>
+        <v>8.965517241379311</v>
       </c>
       <c r="M52" t="n">
-        <v>205</v>
+        <v>65</v>
       </c>
       <c r="N52" t="n">
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>176.7241379310345</v>
+        <v>56.03448275862069</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EHC 03</t>
+          <t>EG 02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">EPOXY-HOJUELA (combinación) </t>
+          <t>EPOXY-GRANO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>25 a 175 kg</t>
+          <t>22.7 a 24.3 kg</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -3301,30 +3301,30 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>172.4137931034483</v>
+        <v>47.41379310344828</v>
       </c>
       <c r="L53" t="n">
-        <v>27.58620689655173</v>
+        <v>7.586206896551724</v>
       </c>
       <c r="M53" t="n">
-        <v>200.0000000000001</v>
+        <v>55</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>172.4137931034483</v>
+        <v>47.41379310344828</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EG 01</t>
+          <t>EGC 01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EPOXY-GRANO</t>
+          <t>EPOXY-GRANO (combinación)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3356,30 +3356,30 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>56.03448275862069</v>
+        <v>77.58620689655173</v>
       </c>
       <c r="L54" t="n">
-        <v>8.965517241379311</v>
+        <v>12.41379310344828</v>
       </c>
       <c r="M54" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>56.03448275862069</v>
+        <v>77.58620689655173</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EG 02</t>
+          <t>EGC 02</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EPOXY-GRANO</t>
+          <t>EPOXY-GRANO (combinación)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3411,35 +3411,35 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>47.41379310344828</v>
+        <v>60.3448275862069</v>
       </c>
       <c r="L55" t="n">
-        <v>7.586206896551724</v>
+        <v>9.655172413793103</v>
       </c>
       <c r="M55" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>47.41379310344828</v>
+        <v>60.3448275862069</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EGC 01</t>
+          <t>EMI 01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EPOXY-GRANO (combinación)</t>
+          <t>EPOXY-MICA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1 a 20 kg</t>
+          <t>1 kg</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -3466,35 +3466,35 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>77.58620689655173</v>
+        <v>405.1724137931035</v>
       </c>
       <c r="L56" t="n">
-        <v>12.41379310344828</v>
+        <v>64.82758620689656</v>
       </c>
       <c r="M56" t="n">
-        <v>90</v>
+        <v>470.0000000000001</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>77.58620689655173</v>
+        <v>405.1724137931035</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EGC 02</t>
+          <t>EMI 02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EPOXY-GRANO (combinación)</t>
+          <t>EPOXY-MICA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>22.7 a 24.3 kg</t>
+          <t>1/2 kg</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -3521,30 +3521,30 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>60.3448275862069</v>
+        <v>715.5172413793103</v>
       </c>
       <c r="L57" t="n">
-        <v>9.655172413793103</v>
+        <v>114.4827586206897</v>
       </c>
       <c r="M57" t="n">
-        <v>70</v>
+        <v>830</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>60.3448275862069</v>
+        <v>715.5172413793103</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EMI 01</t>
+          <t>EMC 01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EPOXY-MICA</t>
+          <t>EPOXY-MICA (combinado)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3576,30 +3576,30 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>405.1724137931035</v>
+        <v>426.7241379310345</v>
       </c>
       <c r="L58" t="n">
-        <v>64.82758620689656</v>
+        <v>68.27586206896552</v>
       </c>
       <c r="M58" t="n">
-        <v>470.0000000000001</v>
+        <v>495</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>405.1724137931035</v>
+        <v>426.7241379310345</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EMI 02</t>
+          <t>EMC 02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EPOXY-MICA</t>
+          <t>EPOXY-MICA (combinado)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3631,36 +3631,34 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>715.5172413793103</v>
+        <v>737.0689655172414</v>
       </c>
       <c r="L59" t="n">
-        <v>114.4827586206897</v>
+        <v>117.9310344827586</v>
       </c>
       <c r="M59" t="n">
-        <v>830</v>
+        <v>855</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>715.5172413793103</v>
+        <v>737.0689655172414</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EMC 01</t>
+          <t>EPA 01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EPOXY-MICA (combinado)</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1 kg</t>
-        </is>
+          <t>EPO-PAINT (A y B)</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
       </c>
       <c r="D60" t="n">
         <v>5</v>
@@ -3686,36 +3684,34 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>426.7241379310345</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>68.27586206896552</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>495</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>426.7241379310345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EMC 02</t>
+          <t>AS 01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EPOXY-MICA (combinado)</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>1/2 kg</t>
-        </is>
+          <t>ARENA SILICA</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
       </c>
       <c r="D61" t="n">
         <v>5</v>
@@ -3741,34 +3737,36 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>737.0689655172414</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>117.9310344827586</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>855</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>737.0689655172414</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EPA 01</t>
+          <t>RP 01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EPO-PAINT (A y B)</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>0</v>
+          <t>RODILLO DE PICOS EPOXY-PISOS</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1 Pz</t>
+        </is>
       </c>
       <c r="D62" t="n">
         <v>5</v>
@@ -3791,37 +3789,39 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>474.06</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>426.7241379310345</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>68.27586206896547</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>495</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>426.7241379310345</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AS 01</t>
+          <t>JEP 01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ARENA SILICA</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>0</v>
+          <t>JALADOR EPÓXICO PREMIUM</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1 Pz</t>
+        </is>
       </c>
       <c r="D63" t="n">
         <v>5</v>
@@ -3844,33 +3844,33 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>406.09</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>366.3793103448277</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>58.62068965517238</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>425.0000000000001</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>366.3793103448277</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>RP 01</t>
+          <t>JEE 01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RODILLO DE PICOS EPOXY-PISOS</t>
+          <t>JALADOR PARA EPÓXICOS ECO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3899,33 +3899,33 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>426.7241379310345</v>
+        <v>64.65517241379312</v>
       </c>
       <c r="L64" t="n">
-        <v>68.27586206896552</v>
+        <v>10.34482758620689</v>
       </c>
       <c r="M64" t="n">
-        <v>495</v>
+        <v>75.00000000000001</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>426.7241379310345</v>
+        <v>64.65517241379312</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>JEP 01</t>
+          <t>JNE 01</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JALADOR EPÓXICO PREMIUM</t>
+          <t>JALADOR NIVELADOR EPÓXICO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3957,30 +3957,30 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>366.3793103448276</v>
+        <v>1370.689655172414</v>
       </c>
       <c r="L65" t="n">
-        <v>58.62068965517242</v>
+        <v>219.3103448275862</v>
       </c>
       <c r="M65" t="n">
-        <v>425.0000000000001</v>
+        <v>1590</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>366.3793103448276</v>
+        <v>1370.689655172414</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>JEE 01</t>
+          <t>JD 01</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JALADOR PARA EPÓXICOS ECO</t>
+          <t>JALADOR DENTADO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4009,33 +4009,33 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>370.51</v>
       </c>
       <c r="K66" t="n">
-        <v>64.65517241379311</v>
+        <v>336.2068965517242</v>
       </c>
       <c r="L66" t="n">
-        <v>10.3448275862069</v>
+        <v>53.79310344827587</v>
       </c>
       <c r="M66" t="n">
-        <v>75.00000000000001</v>
+        <v>390.0000000000001</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>64.65517241379311</v>
+        <v>336.2068965517242</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>JNE 01</t>
+          <t>CV 01</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JALADOR NIVELADOR EPÓXICO</t>
+          <t>CUÑA PARA VINIL</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4064,33 +4064,33 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>62.71</v>
       </c>
       <c r="K67" t="n">
-        <v>1370.689655172414</v>
+        <v>56.03448275862069</v>
       </c>
       <c r="L67" t="n">
-        <v>219.3103448275862</v>
+        <v>8.96551724137931</v>
       </c>
       <c r="M67" t="n">
-        <v>1590</v>
+        <v>65</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>1370.689655172414</v>
+        <v>56.03448275862069</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>JD 01</t>
+          <t>R 01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JALADOR DENTADO</t>
+          <t>RODILLO 4"</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4119,33 +4119,33 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>77.92</v>
       </c>
       <c r="K68" t="n">
-        <v>336.2068965517242</v>
+        <v>68.96551724137932</v>
       </c>
       <c r="L68" t="n">
-        <v>53.79310344827587</v>
+        <v>11.03448275862068</v>
       </c>
       <c r="M68" t="n">
-        <v>390.0000000000001</v>
+        <v>80</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>336.2068965517242</v>
+        <v>68.96551724137932</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CV 01</t>
+          <t>R 02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CUÑA PARA VINIL</t>
+          <t>RODILLO 9"</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4174,33 +4174,33 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>193.32</v>
       </c>
       <c r="K69" t="n">
-        <v>56.03448275862069</v>
+        <v>172.4137931034484</v>
       </c>
       <c r="L69" t="n">
-        <v>8.965517241379311</v>
+        <v>27.58620689655172</v>
       </c>
       <c r="M69" t="n">
-        <v>65</v>
+        <v>200.0000000000001</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>56.03448275862069</v>
+        <v>172.4137931034484</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>R 01</t>
+          <t>F 01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RODILLO 4"</t>
+          <t>FELPA 4"</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4229,33 +4229,33 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>38.01</v>
       </c>
       <c r="K70" t="n">
-        <v>68.96551724137932</v>
+        <v>34.48275862068966</v>
       </c>
       <c r="L70" t="n">
-        <v>11.03448275862069</v>
+        <v>5.517241379310342</v>
       </c>
       <c r="M70" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="N70" t="n">
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>68.96551724137932</v>
+        <v>34.48275862068966</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>R 02</t>
+          <t>F 02</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RODILLO 9"</t>
+          <t>FELPA 9"</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4284,33 +4284,33 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>133.02</v>
       </c>
       <c r="K71" t="n">
-        <v>172.4137931034483</v>
+        <v>120.6896551724138</v>
       </c>
       <c r="L71" t="n">
-        <v>27.58620689655173</v>
+        <v>19.31034482758619</v>
       </c>
       <c r="M71" t="n">
-        <v>200.0000000000001</v>
+        <v>140</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>172.4137931034483</v>
+        <v>120.6896551724138</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>F 01</t>
+          <t>M 01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FELPA 4"</t>
+          <t>MEZCLADOR</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4342,30 +4342,30 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>34.48275862068966</v>
+        <v>163.7931034482759</v>
       </c>
       <c r="L72" t="n">
-        <v>5.517241379310345</v>
+        <v>26.20689655172415</v>
       </c>
       <c r="M72" t="n">
-        <v>40</v>
+        <v>190.0000000000001</v>
       </c>
       <c r="N72" t="n">
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>34.48275862068966</v>
+        <v>163.7931034482759</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>F 02</t>
+          <t>ES 01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FELPA 9"</t>
+          <t>EPOXI SPIKES UNITALLA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4394,33 +4394,33 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>660.26</v>
       </c>
       <c r="K73" t="n">
-        <v>120.6896551724138</v>
+        <v>599.1379310344828</v>
       </c>
       <c r="L73" t="n">
-        <v>19.31034482758621</v>
+        <v>95.86206896551721</v>
       </c>
       <c r="M73" t="n">
-        <v>140</v>
+        <v>695</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>120.6896551724138</v>
+        <v>599.1379310344828</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>M 01</t>
+          <t>KB 01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MEZCLADOR</t>
+          <t>KIT DE BORLAS PARA PULIMENTO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4449,33 +4449,33 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>418</v>
       </c>
       <c r="K74" t="n">
-        <v>163.7931034482759</v>
+        <v>379.3103448275862</v>
       </c>
       <c r="L74" t="n">
-        <v>26.20689655172415</v>
+        <v>60.68965517241378</v>
       </c>
       <c r="M74" t="n">
-        <v>190.0000000000001</v>
+        <v>440</v>
       </c>
       <c r="N74" t="n">
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>163.7931034482759</v>
+        <v>379.3103448275862</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ES 01</t>
+          <t>CD 01</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EPOXI SPIKES UNITALLA</t>
+          <t>COPA DIAMANTE PARA DESBASTE 7"</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4507,30 +4507,30 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>599.1379310344828</v>
+        <v>1650.862068965517</v>
       </c>
       <c r="L75" t="n">
-        <v>95.86206896551725</v>
+        <v>264.1379310344827</v>
       </c>
       <c r="M75" t="n">
-        <v>695</v>
+        <v>1915</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>599.1379310344828</v>
+        <v>1650.862068965517</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>KB 01</t>
+          <t>EB 01</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>KIT DE BORLAS PARA PULIMENTO</t>
+          <t>EPOXI BUBLES</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4559,33 +4559,33 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>74.81</v>
       </c>
       <c r="K76" t="n">
-        <v>379.3103448275862</v>
+        <v>77.58620689655173</v>
       </c>
       <c r="L76" t="n">
-        <v>60.68965517241379</v>
+        <v>12.41379310344827</v>
       </c>
       <c r="M76" t="n">
-        <v>440</v>
+        <v>90</v>
       </c>
       <c r="N76" t="n">
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>379.3103448275862</v>
+        <v>77.58620689655173</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CD 01</t>
+          <t>BD 01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>COPA DIAMANTE PARA DESBASTE 7"</t>
+          <t>BÁSCULA DIGITAL CAPACIDAD 5kg</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4617,30 +4617,30 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>1650.862068965517</v>
+        <v>215.5172413793103</v>
       </c>
       <c r="L77" t="n">
-        <v>264.1379310344827</v>
+        <v>34.48275862068964</v>
       </c>
       <c r="M77" t="n">
-        <v>1915</v>
+        <v>249.9999999999999</v>
       </c>
       <c r="N77" t="n">
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>1650.862068965517</v>
+        <v>215.5172413793103</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EB 01</t>
+          <t>LPE 01</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EPOXI BUBLES</t>
+          <t>LIJADORA DE PISO ELÉCTRICA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4669,38 +4669,38 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>3452.64</v>
       </c>
       <c r="K78" t="n">
-        <v>77.58620689655173</v>
+        <v>3447.413793103448</v>
       </c>
       <c r="L78" t="n">
-        <v>12.41379310344828</v>
+        <v>551.5862068965516</v>
       </c>
       <c r="M78" t="n">
-        <v>90</v>
+        <v>3999</v>
       </c>
       <c r="N78" t="n">
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>77.58620689655173</v>
+        <v>3447.413793103448</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BD 01</t>
+          <t>CN 01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BÁSCULA DIGITAL CAPACIDAD 5kg</t>
+          <t>CÁSCARA DE NARANJA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1 Pz</t>
+          <t>0 a 3.999 kg</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -4724,77 +4724,627 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>444.45</v>
       </c>
       <c r="K79" t="n">
-        <v>215.5172413793103</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>34.48275862068964</v>
+        <v>79.99999999999994</v>
       </c>
       <c r="M79" t="n">
-        <v>249.9999999999999</v>
+        <v>580</v>
       </c>
       <c r="N79" t="n">
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>215.5172413793103</v>
+        <v>500.0000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LPE 01</t>
+          <t>CN 02</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LIJADORA DE PISO ELÉCTRICA</t>
+          <t>CÁSCARA DE NARANJA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>4 a 7.999 kg</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>5</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>⚠️ REABASTECER</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>433.74</v>
+      </c>
+      <c r="K80" t="n">
+        <v>482.7586206896552</v>
+      </c>
+      <c r="L80" t="n">
+        <v>77.24137931034477</v>
+      </c>
+      <c r="M80" t="n">
+        <v>560</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>482.7586206896552</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>CN 03</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CÁSCARA DE NARANJA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>8 a 19.999 kg</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>5</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>⚠️ REABASTECER</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>423.54</v>
+      </c>
+      <c r="K81" t="n">
+        <v>465.5172413793103</v>
+      </c>
+      <c r="L81" t="n">
+        <v>74.48275862068965</v>
+      </c>
+      <c r="M81" t="n">
+        <v>540</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>465.5172413793103</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>CN 04</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>CÁSCARA DE NARANJA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>+ 20 kg</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>5</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>⚠️ REABASTECER</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>413.8</v>
+      </c>
+      <c r="K82" t="n">
+        <v>448.2758620689655</v>
+      </c>
+      <c r="L82" t="n">
+        <v>71.72413793103448</v>
+      </c>
+      <c r="M82" t="n">
+        <v>520</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>448.2758620689655</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ESV 01</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ESTUCO VENECIANO</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>5</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>⚠️ REABASTECER</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>400</v>
+      </c>
+      <c r="K83" t="n">
+        <v>413.7931034482759</v>
+      </c>
+      <c r="L83" t="n">
+        <v>66.20689655172413</v>
+      </c>
+      <c r="M83" t="n">
+        <v>480</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>413.7931034482759</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ESV 02</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ESTUCO VENECIANO</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>4 L</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>5</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>⚠️ REABASTECER</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>380</v>
+      </c>
+      <c r="K84" t="n">
+        <v>396.551724137931</v>
+      </c>
+      <c r="L84" t="n">
+        <v>63.44827586206895</v>
+      </c>
+      <c r="M84" t="n">
+        <v>460</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>396.551724137931</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ESV 03</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ESTUCO VENECIANO</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>19 L</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>5</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>⚠️ REABASTECER</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>361</v>
+      </c>
+      <c r="K85" t="n">
+        <v>379.3103448275862</v>
+      </c>
+      <c r="L85" t="n">
+        <v>60.68965517241378</v>
+      </c>
+      <c r="M85" t="n">
+        <v>440</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>379.3103448275862</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>GW 01</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>GRANO WALL</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>4 L</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>5</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>⚠️ REABASTECER</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>231.58</v>
+      </c>
+      <c r="K86" t="n">
+        <v>237.0689655172414</v>
+      </c>
+      <c r="L86" t="n">
+        <v>37.93103448275861</v>
+      </c>
+      <c r="M86" t="n">
+        <v>275</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>237.0689655172414</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>GW 02</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>GRANO WALL</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>19 L</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>5</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>⚠️ REABASTECER</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>182.83</v>
+      </c>
+      <c r="K87" t="n">
+        <v>193.9655172413793</v>
+      </c>
+      <c r="L87" t="n">
+        <v>31.03448275862067</v>
+      </c>
+      <c r="M87" t="n">
+        <v>225</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>193.9655172413793</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>EC 01</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>EPOXY CUARZO</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>0 a 59.999 kg</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>5</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>⚠️ REABASTECER</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>29.34</v>
+      </c>
+      <c r="K88" t="n">
+        <v>30.17241379310345</v>
+      </c>
+      <c r="L88" t="n">
+        <v>4.827586206896548</v>
+      </c>
+      <c r="M88" t="n">
+        <v>35</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>30.17241379310345</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>EC 02</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>EPOXY CUARZO</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>+ 60 kg</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>5</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>⚠️ REABASTECER</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>29.34</v>
+      </c>
+      <c r="K89" t="n">
+        <v>25.86206896551724</v>
+      </c>
+      <c r="L89" t="n">
+        <v>4.137931034482758</v>
+      </c>
+      <c r="M89" t="n">
+        <v>30</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>25.86206896551724</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ESP 01</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>EPOXY SPIKES PREMIUM</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
           <t>1 Pz</t>
         </is>
       </c>
-      <c r="D80" t="n">
-        <v>5</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>⚠️ REABASTECER</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
+      <c r="D90" t="n">
+        <v>5</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>⚠️ REABASTECER</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>2373.11</v>
+      </c>
+      <c r="K90" t="n">
+        <v>2153.448275862069</v>
+      </c>
+      <c r="L90" t="n">
+        <v>344.5517241379307</v>
+      </c>
+      <c r="M90" t="n">
+        <v>2498</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>2153.448275862069</v>
       </c>
     </row>
   </sheetData>
@@ -5229,7 +5779,7 @@
         <v>1.5</v>
       </c>
       <c r="D2" t="n">
-        <v>695</v>
+        <v>720</v>
       </c>
       <c r="E2" t="n">
         <v>1.2</v>
@@ -5251,7 +5801,7 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>1315</v>
+        <v>1440</v>
       </c>
       <c r="E3" t="n">
         <v>1.2</v>
@@ -5273,7 +5823,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>2520</v>
+        <v>2760</v>
       </c>
       <c r="E4" t="n">
         <v>1.2</v>
@@ -5295,7 +5845,7 @@
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>4040</v>
+        <v>4400</v>
       </c>
       <c r="E5" t="n">
         <v>1.2</v>
@@ -5317,7 +5867,7 @@
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>5835</v>
+        <v>6300</v>
       </c>
       <c r="E6" t="n">
         <v>1.2</v>
@@ -5339,7 +5889,7 @@
         <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>7490</v>
+        <v>8000</v>
       </c>
       <c r="E7" t="n">
         <v>1.2</v>
@@ -5361,7 +5911,7 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>950</v>
+        <v>960</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -5383,7 +5933,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>2705</v>
+        <v>2760</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -5405,7 +5955,7 @@
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>4285</v>
+        <v>4400</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -5427,7 +5977,7 @@
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>7735</v>
+        <v>7980</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -5449,7 +5999,7 @@
         <v>1.42</v>
       </c>
       <c r="D12" t="n">
-        <v>770</v>
+        <v>795</v>
       </c>
       <c r="E12" t="n">
         <v>1.07</v>
@@ -5471,7 +6021,7 @@
         <v>4.26</v>
       </c>
       <c r="D13" t="n">
-        <v>2200</v>
+        <v>2386</v>
       </c>
       <c r="E13" t="n">
         <v>1.07</v>
@@ -5493,7 +6043,7 @@
         <v>7.1</v>
       </c>
       <c r="D14" t="n">
-        <v>3555</v>
+        <v>3692</v>
       </c>
       <c r="E14" t="n">
         <v>1.07</v>
@@ -5515,7 +6065,7 @@
         <v>17.04</v>
       </c>
       <c r="D15" t="n">
-        <v>8245</v>
+        <v>8520</v>
       </c>
       <c r="E15" t="n">
         <v>1.07</v>
@@ -5559,7 +6109,7 @@
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>3540</v>
+        <v>3800</v>
       </c>
       <c r="E17" t="n">
         <v>0.3333</v>
@@ -5581,7 +6131,7 @@
         <v>20.025</v>
       </c>
       <c r="D18" t="n">
-        <v>6720</v>
+        <v>7409</v>
       </c>
       <c r="E18" t="n">
         <v>0.3333</v>
@@ -5603,7 +6153,7 @@
         <v>1.333</v>
       </c>
       <c r="D19" t="n">
-        <v>615</v>
+        <v>640</v>
       </c>
       <c r="E19" t="n">
         <v>1.07</v>
@@ -5625,7 +6175,7 @@
         <v>6.65</v>
       </c>
       <c r="D20" t="n">
-        <v>2930</v>
+        <v>3192</v>
       </c>
       <c r="E20" t="n">
         <v>1.07</v>
@@ -5647,7 +6197,7 @@
         <v>13.3</v>
       </c>
       <c r="D21" t="n">
-        <v>5585</v>
+        <v>5852</v>
       </c>
       <c r="E21" t="n">
         <v>1.07</v>
@@ -5669,7 +6219,7 @@
         <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>9600</v>
+        <v>10080</v>
       </c>
       <c r="E22" t="n">
         <v>1.07</v>
@@ -5801,7 +6351,7 @@
         <v>100</v>
       </c>
       <c r="D28" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -5823,7 +6373,7 @@
         <v>250</v>
       </c>
       <c r="D29" t="n">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -5845,7 +6395,7 @@
         <v>500</v>
       </c>
       <c r="D30" t="n">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -5867,7 +6417,7 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -5889,7 +6439,7 @@
         <v>20</v>
       </c>
       <c r="D32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -5911,7 +6461,7 @@
         <v>60</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -5933,7 +6483,7 @@
         <v>100</v>
       </c>
       <c r="D34" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
@@ -5955,7 +6505,7 @@
         <v>250</v>
       </c>
       <c r="D35" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -5977,7 +6527,7 @@
         <v>500</v>
       </c>
       <c r="D36" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>

--- a/Sistema_Inventario_NEMET_Final.xlsx
+++ b/Sistema_Inventario_NEMET_Final.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Cat_Productos" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Clientes" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Historial_Cotizaciones" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Escalas_Precios_KG" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6864,4 +6865,1195 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Producto_Proveedor</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Producto_NEMET</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Rango_Desde_Kg</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rango_Hasta_Kg</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Costo_Compra_IVA_por_Kg</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Precio_Publico_por_Kg</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Margen_por_Kg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Margen_Porcentaje_Sobre_Venta</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Margen_Markup_Sobre_Costo</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Rango_Texto_Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EPOXY PISOS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EPOXY PISOS (A Y B) TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>361.42</v>
+      </c>
+      <c r="F2" t="n">
+        <v>480</v>
+      </c>
+      <c r="G2" t="n">
+        <v>118.58</v>
+      </c>
+      <c r="H2" t="n">
+        <v>24.70416666666666</v>
+      </c>
+      <c r="I2" t="n">
+        <v>32.80947374246029</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0 - 5.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EPOXY PISOS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EPOXY PISOS (A Y B) TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9.999000000000001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>346.02</v>
+      </c>
+      <c r="F3" t="n">
+        <v>460</v>
+      </c>
+      <c r="G3" t="n">
+        <v>113.98</v>
+      </c>
+      <c r="H3" t="n">
+        <v>24.77826086956522</v>
+      </c>
+      <c r="I3" t="n">
+        <v>32.94029246864344</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6 - 9.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EPOXY PISOS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EPOXY PISOS (A Y B) TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>14.999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>332.95</v>
+      </c>
+      <c r="F4" t="n">
+        <v>440</v>
+      </c>
+      <c r="G4" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="H4" t="n">
+        <v>24.32954545454546</v>
+      </c>
+      <c r="I4" t="n">
+        <v>32.15197477098664</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>10 - 14.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>EPOXY PISOS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EPOXY PISOS (A Y B) TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="n">
+        <v>19.999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>420</v>
+      </c>
+      <c r="G5" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>24.57142857142857</v>
+      </c>
+      <c r="I5" t="n">
+        <v>32.57575757575757</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15 - 19.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EPOXY PISOS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EPOXY PISOS (A Y B) TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" t="n">
+        <v>301.45</v>
+      </c>
+      <c r="F6" t="n">
+        <v>400</v>
+      </c>
+      <c r="G6" t="n">
+        <v>98.55000000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>24.6375</v>
+      </c>
+      <c r="I6" t="n">
+        <v>32.69198872118096</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>+ 20 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EPOXY PRIMER</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EPOXY PRIMER (A Y B) TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9.999000000000001</v>
+      </c>
+      <c r="E7" t="n">
+        <v>397.99</v>
+      </c>
+      <c r="F7" t="n">
+        <v>400</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.009999999999991</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5024999999999977</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.5050378150204756</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0 - 9.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EPOXY PRIMER</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>EPOXY PRIMER (A Y B) TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>19.999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>292.7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>380</v>
+      </c>
+      <c r="G8" t="n">
+        <v>87.30000000000001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>22.97368421052632</v>
+      </c>
+      <c r="I8" t="n">
+        <v>29.82576016399044</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10 - 19.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EPOXY PRIMER</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EPOXY PRIMER (A Y B) TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>20</v>
+      </c>
+      <c r="E9" t="n">
+        <v>276.35</v>
+      </c>
+      <c r="F9" t="n">
+        <v>370</v>
+      </c>
+      <c r="G9" t="n">
+        <v>93.64999999999998</v>
+      </c>
+      <c r="H9" t="n">
+        <v>25.3108108108108</v>
+      </c>
+      <c r="I9" t="n">
+        <v>33.88818527229961</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>+ 20 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CÁSCARA DE NARANJA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CÁSCARA DE NARANJA</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.999</v>
+      </c>
+      <c r="E10" t="n">
+        <v>444.45</v>
+      </c>
+      <c r="F10" t="n">
+        <v>580</v>
+      </c>
+      <c r="G10" t="n">
+        <v>135.55</v>
+      </c>
+      <c r="H10" t="n">
+        <v>23.37068965517242</v>
+      </c>
+      <c r="I10" t="n">
+        <v>30.49836877039037</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0 - 3.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CÁSCARA DE NARANJA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CÁSCARA DE NARANJA</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7.999</v>
+      </c>
+      <c r="E11" t="n">
+        <v>433.74</v>
+      </c>
+      <c r="F11" t="n">
+        <v>560</v>
+      </c>
+      <c r="G11" t="n">
+        <v>126.26</v>
+      </c>
+      <c r="H11" t="n">
+        <v>22.54642857142857</v>
+      </c>
+      <c r="I11" t="n">
+        <v>29.10960483238807</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4 - 7.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CÁSCARA DE NARANJA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CÁSCARA DE NARANJA</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>19.999</v>
+      </c>
+      <c r="E12" t="n">
+        <v>423.54</v>
+      </c>
+      <c r="F12" t="n">
+        <v>540</v>
+      </c>
+      <c r="G12" t="n">
+        <v>116.46</v>
+      </c>
+      <c r="H12" t="n">
+        <v>21.56666666666666</v>
+      </c>
+      <c r="I12" t="n">
+        <v>27.4968125796855</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>8 - 19.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CÁSCARA DE NARANJA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CÁSCARA DE NARANJA</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E13" t="n">
+        <v>413.8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>520</v>
+      </c>
+      <c r="G13" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>20.42307692307692</v>
+      </c>
+      <c r="I13" t="n">
+        <v>25.66457225712904</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>+ 20 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EPO-DEEP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>EPO-DEEP TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.299</v>
+      </c>
+      <c r="E14" t="n">
+        <v>461.88</v>
+      </c>
+      <c r="F14" t="n">
+        <v>560</v>
+      </c>
+      <c r="G14" t="n">
+        <v>98.12</v>
+      </c>
+      <c r="H14" t="n">
+        <v>17.52142857142857</v>
+      </c>
+      <c r="I14" t="n">
+        <v>21.24361305966918</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0 - 4.299 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EPO-DEEP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>EPO-DEEP TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7.099</v>
+      </c>
+      <c r="E15" t="n">
+        <v>437.44</v>
+      </c>
+      <c r="F15" t="n">
+        <v>540</v>
+      </c>
+      <c r="G15" t="n">
+        <v>102.56</v>
+      </c>
+      <c r="H15" t="n">
+        <v>18.99259259259259</v>
+      </c>
+      <c r="I15" t="n">
+        <v>23.44550109729335</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4.3 - 7.099 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EPO-DEEP</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>EPO-DEEP TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>16.999</v>
+      </c>
+      <c r="E16" t="n">
+        <v>424.71</v>
+      </c>
+      <c r="F16" t="n">
+        <v>520</v>
+      </c>
+      <c r="G16" t="n">
+        <v>95.29000000000002</v>
+      </c>
+      <c r="H16" t="n">
+        <v>18.32500000000001</v>
+      </c>
+      <c r="I16" t="n">
+        <v>22.43648607284971</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>7.1 - 16.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EPO-DEEP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EPO-DEEP TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>17</v>
+      </c>
+      <c r="E17" t="n">
+        <v>389.43</v>
+      </c>
+      <c r="F17" t="n">
+        <v>500</v>
+      </c>
+      <c r="G17" t="n">
+        <v>110.57</v>
+      </c>
+      <c r="H17" t="n">
+        <v>22.114</v>
+      </c>
+      <c r="I17" t="n">
+        <v>28.39277919009835</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>+ 17 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EPO-DEEP ULTRA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>EPO-DEEP ULTRA (A Y B) TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6.699</v>
+      </c>
+      <c r="E18" t="n">
+        <v>392.24</v>
+      </c>
+      <c r="F18" t="n">
+        <v>480</v>
+      </c>
+      <c r="G18" t="n">
+        <v>87.75999999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>18.28333333333333</v>
+      </c>
+      <c r="I18" t="n">
+        <v>22.3740566999796</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0 - 6.699 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EPO-DEEP ULTRA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>EPO-DEEP ULTRA (A Y B) TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>13.299</v>
+      </c>
+      <c r="E19" t="n">
+        <v>373.55</v>
+      </c>
+      <c r="F19" t="n">
+        <v>460</v>
+      </c>
+      <c r="G19" t="n">
+        <v>86.44999999999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>18.79347826086956</v>
+      </c>
+      <c r="I19" t="n">
+        <v>23.14281889974568</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>6.7 - 13.299 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EPO-DEEP ULTRA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>EPO-DEEP ULTRA (A Y B) TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>23.999</v>
+      </c>
+      <c r="E20" t="n">
+        <v>355.77</v>
+      </c>
+      <c r="F20" t="n">
+        <v>440</v>
+      </c>
+      <c r="G20" t="n">
+        <v>84.23000000000002</v>
+      </c>
+      <c r="H20" t="n">
+        <v>19.14318181818182</v>
+      </c>
+      <c r="I20" t="n">
+        <v>23.67540826938753</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>13.3 - 23.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EPO-DEEP ULTRA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>EPO-DEEP ULTRA (A Y B) TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>24</v>
+      </c>
+      <c r="E21" t="n">
+        <v>325.58</v>
+      </c>
+      <c r="F21" t="n">
+        <v>420</v>
+      </c>
+      <c r="G21" t="n">
+        <v>94.42000000000002</v>
+      </c>
+      <c r="H21" t="n">
+        <v>22.48095238095238</v>
+      </c>
+      <c r="I21" t="n">
+        <v>29.00055285951226</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>+ 24 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EPO-FAST</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>EPO-FAST (A Y B) TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5.999</v>
+      </c>
+      <c r="E22" t="n">
+        <v>392.24</v>
+      </c>
+      <c r="F22" t="n">
+        <v>480</v>
+      </c>
+      <c r="G22" t="n">
+        <v>87.75999999999999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>18.28333333333333</v>
+      </c>
+      <c r="I22" t="n">
+        <v>22.3740566999796</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0 - 5.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EPO-FAST</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>EPO-FAST (A Y B) TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>9.999000000000001</v>
+      </c>
+      <c r="E23" t="n">
+        <v>373.55</v>
+      </c>
+      <c r="F23" t="n">
+        <v>460</v>
+      </c>
+      <c r="G23" t="n">
+        <v>86.44999999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>18.79347826086956</v>
+      </c>
+      <c r="I23" t="n">
+        <v>23.14281889974568</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>6 - 9.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EPO-FAST</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EPO-FAST (A Y B) TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" t="n">
+        <v>18.999</v>
+      </c>
+      <c r="E24" t="n">
+        <v>355.77</v>
+      </c>
+      <c r="F24" t="n">
+        <v>440</v>
+      </c>
+      <c r="G24" t="n">
+        <v>84.23000000000002</v>
+      </c>
+      <c r="H24" t="n">
+        <v>19.14318181818182</v>
+      </c>
+      <c r="I24" t="n">
+        <v>23.67540826938753</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>10 - 18.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EPO-FAST</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EPO-FAST (A Y B) TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>19</v>
+      </c>
+      <c r="E25" t="n">
+        <v>325.58</v>
+      </c>
+      <c r="F25" t="n">
+        <v>420</v>
+      </c>
+      <c r="G25" t="n">
+        <v>94.42000000000002</v>
+      </c>
+      <c r="H25" t="n">
+        <v>22.48095238095238</v>
+      </c>
+      <c r="I25" t="n">
+        <v>29.00055285951226</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>+ 19 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>EPOXY-HOJUELA (1 color)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>EPOXY-HOJUELA (1 color)</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>59.999</v>
+      </c>
+      <c r="E26" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="F26" t="n">
+        <v>205</v>
+      </c>
+      <c r="G26" t="n">
+        <v>22.30000000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>10.87804878048781</v>
+      </c>
+      <c r="I26" t="n">
+        <v>12.20580186097428</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0 - 59.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>EPOXY-HOJUELA (1 color)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>EPOXY-HOJUELA (1 color)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>60</v>
+      </c>
+      <c r="E27" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="F27" t="n">
+        <v>200</v>
+      </c>
+      <c r="G27" t="n">
+        <v>17.30000000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>8.650000000000006</v>
+      </c>
+      <c r="I27" t="n">
+        <v>9.469074986316372</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>+ 60 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>EPOXY-HOJUELA (combinación)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>EPOXY-HOJUELA (combinación)</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>59.999</v>
+      </c>
+      <c r="E28" t="n">
+        <v>214.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>235</v>
+      </c>
+      <c r="G28" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>8.723404255319149</v>
+      </c>
+      <c r="I28" t="n">
+        <v>9.557109557109557</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0 - 59.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>EPOXY-HOJUELA (combinación)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>EPOXY-HOJUELA (combinación)</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>60</v>
+      </c>
+      <c r="E29" t="n">
+        <v>214.5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>230</v>
+      </c>
+      <c r="G29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>6.739130434782608</v>
+      </c>
+      <c r="I29" t="n">
+        <v>7.226107226107226</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>+ 60 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>EPOXY CUARZO</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>EPOXY CUARZO</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>59.999</v>
+      </c>
+      <c r="E30" t="n">
+        <v>29.34</v>
+      </c>
+      <c r="F30" t="n">
+        <v>35</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="H30" t="n">
+        <v>16.17142857142857</v>
+      </c>
+      <c r="I30" t="n">
+        <v>19.29107021131561</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0 - 59.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EPOXY CUARZO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>EPOXY CUARZO</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>60</v>
+      </c>
+      <c r="E31" t="n">
+        <v>29.34</v>
+      </c>
+      <c r="F31" t="n">
+        <v>30</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.6600000000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.200000000000001</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.249488752556238</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>+ 60 kg</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Sistema_Inventario_NEMET_Final.xlsx
+++ b/Sistema_Inventario_NEMET_Final.xlsx
@@ -5735,7 +5735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5769,6 +5769,16 @@
           <t>Prop_B</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Dosis_g_m2</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Fuente_Dosis</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6332,15 +6342,20 @@
       <c r="D27" t="n">
         <v>75</v>
       </c>
-      <c r="E27" t="n">
-        <v>1</v>
-      </c>
       <c r="F27" t="n">
         <v>100</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
+      <c r="H27" t="n">
+        <v>10</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Manual NEMET: 10 g/m²</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6354,15 +6369,20 @@
       <c r="D28" t="n">
         <v>112</v>
       </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
       <c r="F28" t="n">
         <v>100</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
+      <c r="H28" t="n">
+        <v>10</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Manual NEMET: 10 g/m²</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6376,15 +6396,20 @@
       <c r="D29" t="n">
         <v>270</v>
       </c>
-      <c r="E29" t="n">
-        <v>1</v>
-      </c>
       <c r="F29" t="n">
         <v>100</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
+      <c r="H29" t="n">
+        <v>10</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Manual NEMET: 10 g/m²</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6398,15 +6423,20 @@
       <c r="D30" t="n">
         <v>520</v>
       </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
       <c r="F30" t="n">
         <v>100</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
+      <c r="H30" t="n">
+        <v>10</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Manual NEMET: 10 g/m²</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6420,15 +6450,20 @@
       <c r="D31" t="n">
         <v>840</v>
       </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
       <c r="F31" t="n">
         <v>100</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
+      <c r="H31" t="n">
+        <v>10</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Manual NEMET: 10 g/m²</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6442,15 +6477,20 @@
       <c r="D32" t="n">
         <v>25</v>
       </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
       <c r="F32" t="n">
         <v>100</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
+      <c r="H32" t="n">
+        <v>60</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Referencia de trabajo: ≈60 ml/m² (1 L ≈ 16 m²); ajustar si el manual la especifica</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6464,15 +6504,20 @@
       <c r="D33" t="n">
         <v>65</v>
       </c>
-      <c r="E33" t="n">
-        <v>1</v>
-      </c>
       <c r="F33" t="n">
         <v>100</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
+      <c r="H33" t="n">
+        <v>60</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Referencia de trabajo: ≈60 ml/m² (1 L ≈ 16 m²); ajustar si el manual la especifica</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6486,15 +6531,20 @@
       <c r="D34" t="n">
         <v>110</v>
       </c>
-      <c r="E34" t="n">
-        <v>1</v>
-      </c>
       <c r="F34" t="n">
         <v>100</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
+      <c r="H34" t="n">
+        <v>60</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Referencia de trabajo: ≈60 ml/m² (1 L ≈ 16 m²); ajustar si el manual la especifica</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6508,15 +6558,20 @@
       <c r="D35" t="n">
         <v>190</v>
       </c>
-      <c r="E35" t="n">
-        <v>1</v>
-      </c>
       <c r="F35" t="n">
         <v>100</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
+      <c r="H35" t="n">
+        <v>60</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Referencia de trabajo: ≈60 ml/m² (1 L ≈ 16 m²); ajustar si el manual la especifica</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6530,15 +6585,20 @@
       <c r="D36" t="n">
         <v>320</v>
       </c>
-      <c r="E36" t="n">
-        <v>1</v>
-      </c>
       <c r="F36" t="n">
         <v>100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
+      <c r="H36" t="n">
+        <v>60</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Referencia de trabajo: ≈60 ml/m² (1 L ≈ 16 m²); ajustar si el manual la especifica</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6552,15 +6612,20 @@
       <c r="D37" t="n">
         <v>550</v>
       </c>
-      <c r="E37" t="n">
-        <v>1</v>
-      </c>
       <c r="F37" t="n">
         <v>100</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
+      <c r="H37" t="n">
+        <v>60</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Referencia de trabajo: ≈60 ml/m² (1 L ≈ 16 m²); ajustar si el manual la especifica</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6574,15 +6639,20 @@
       <c r="D38" t="n">
         <v>275</v>
       </c>
-      <c r="E38" t="n">
-        <v>1</v>
-      </c>
       <c r="F38" t="n">
         <v>100</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
+      <c r="H38" t="n">
+        <v>10</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Criterio NEMET para pigmentos en polvo (ajustable)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6596,15 +6666,20 @@
       <c r="D39" t="n">
         <v>630</v>
       </c>
-      <c r="E39" t="n">
-        <v>1</v>
-      </c>
       <c r="F39" t="n">
         <v>100</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
+      <c r="H39" t="n">
+        <v>10</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Criterio NEMET para pigmentos en polvo (ajustable)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6618,15 +6693,20 @@
       <c r="D40" t="n">
         <v>1100</v>
       </c>
-      <c r="E40" t="n">
-        <v>1</v>
-      </c>
       <c r="F40" t="n">
         <v>100</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
+      <c r="H40" t="n">
+        <v>10</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Criterio NEMET para pigmentos en polvo (ajustable)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6640,15 +6720,20 @@
       <c r="D41" t="n">
         <v>106</v>
       </c>
-      <c r="E41" t="n">
-        <v>1</v>
-      </c>
       <c r="F41" t="n">
         <v>100</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
+      <c r="H41" t="n">
+        <v>8</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Manual NEMET: 8 g/m²</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6662,15 +6747,20 @@
       <c r="D42" t="n">
         <v>312</v>
       </c>
-      <c r="E42" t="n">
-        <v>1</v>
-      </c>
       <c r="F42" t="n">
         <v>100</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
+      <c r="H42" t="n">
+        <v>8</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Manual NEMET: 8 g/m²</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6684,15 +6774,20 @@
       <c r="D43" t="n">
         <v>466</v>
       </c>
-      <c r="E43" t="n">
-        <v>1</v>
-      </c>
       <c r="F43" t="n">
         <v>100</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
+      <c r="H43" t="n">
+        <v>8</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Manual NEMET: 8 g/m²</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6706,15 +6801,20 @@
       <c r="D44" t="n">
         <v>844</v>
       </c>
-      <c r="E44" t="n">
-        <v>1</v>
-      </c>
       <c r="F44" t="n">
         <v>100</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
+      <c r="H44" t="n">
+        <v>8</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Manual NEMET: 8 g/m²</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6728,14 +6828,19 @@
       <c r="D45" t="n">
         <v>1504</v>
       </c>
-      <c r="E45" t="n">
-        <v>1</v>
-      </c>
       <c r="F45" t="n">
         <v>100</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>8</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Manual NEMET: 8 g/m²</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Sistema_Inventario_NEMET_Final.xlsx
+++ b/Sistema_Inventario_NEMET_Final.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="243">
   <si>
     <t>CONTROL DE INVENTARIO Y FACTURACIÓN - NEMET</t>
   </si>
@@ -737,9 +737,6 @@
     <t>Herramienta</t>
   </si>
   <si>
-    <t xml:space="preserve">EPOXY PRIMER </t>
-  </si>
-  <si>
     <t>20 KG</t>
   </si>
   <si>
@@ -747,6 +744,15 @@
   </si>
   <si>
     <t>0 - 9,999 KG</t>
+  </si>
+  <si>
+    <t>EPOXY PRIMER 9 Kg</t>
+  </si>
+  <si>
+    <t>EPOXY PRIMER 19 kg</t>
+  </si>
+  <si>
+    <t>EPOXY PRIMER +20 kg</t>
   </si>
 </sst>
 </file>
@@ -4058,10 +4064,10 @@
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C70" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D70">
         <v>5</v>
@@ -4098,10 +4104,10 @@
     </row>
     <row r="71" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C71" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D71">
         <v>5</v>
@@ -4138,10 +4144,10 @@
     </row>
     <row r="72" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
+        <v>242</v>
+      </c>
+      <c r="C72" t="s">
         <v>237</v>
-      </c>
-      <c r="C72" t="s">
-        <v>238</v>
       </c>
       <c r="D72">
         <v>5</v>

--- a/Sistema_Inventario_NEMET_Final.xlsx
+++ b/Sistema_Inventario_NEMET_Final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N90"/>
+  <dimension ref="A1:O90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,6 +506,11 @@
           <t>ValorInventario</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -547,10 +552,10 @@
         <v>655.87</v>
       </c>
       <c r="K3" t="n">
-        <v>685.344827586207</v>
+        <v>685.344828</v>
       </c>
       <c r="L3" t="n">
-        <v>109.655172413793</v>
+        <v>109.655172</v>
       </c>
       <c r="M3" t="n">
         <v>795</v>
@@ -558,6 +563,11 @@
       <c r="N3" t="n">
         <v>0</v>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -599,10 +609,10 @@
         <v>1967.61</v>
       </c>
       <c r="K4" t="n">
-        <v>2056.896551724138</v>
+        <v>2056.896552</v>
       </c>
       <c r="L4" t="n">
-        <v>329.1034482758619</v>
+        <v>329.103448</v>
       </c>
       <c r="M4" t="n">
         <v>2386</v>
@@ -610,6 +620,11 @@
       <c r="N4" t="n">
         <v>0</v>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -651,10 +666,10 @@
         <v>3015.44</v>
       </c>
       <c r="K5" t="n">
-        <v>3182.758620689655</v>
+        <v>3182.758621</v>
       </c>
       <c r="L5" t="n">
-        <v>509.2413793103447</v>
+        <v>509.241379</v>
       </c>
       <c r="M5" t="n">
         <v>3692</v>
@@ -662,6 +677,11 @@
       <c r="N5" t="n">
         <v>0</v>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -703,10 +723,10 @@
         <v>6635.89</v>
       </c>
       <c r="K6" t="n">
-        <v>7344.827586206897</v>
+        <v>7344.827586</v>
       </c>
       <c r="L6" t="n">
-        <v>1175.172413793103</v>
+        <v>1175.172414</v>
       </c>
       <c r="M6" t="n">
         <v>8520</v>
@@ -714,6 +734,11 @@
       <c r="N6" t="n">
         <v>0</v>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -755,10 +780,10 @@
         <v>784.48</v>
       </c>
       <c r="K7" t="n">
-        <v>827.5862068965517</v>
+        <v>827.5862069999999</v>
       </c>
       <c r="L7" t="n">
-        <v>132.4137931034483</v>
+        <v>132.413793</v>
       </c>
       <c r="M7" t="n">
         <v>960</v>
@@ -766,6 +791,11 @@
       <c r="N7" t="n">
         <v>0</v>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -807,10 +837,10 @@
         <v>2241.3</v>
       </c>
       <c r="K8" t="n">
-        <v>2379.310344827587</v>
+        <v>2379.310345</v>
       </c>
       <c r="L8" t="n">
-        <v>380.6896551724135</v>
+        <v>380.689655</v>
       </c>
       <c r="M8" t="n">
         <v>2760</v>
@@ -818,6 +848,11 @@
       <c r="N8" t="n">
         <v>0</v>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -859,10 +894,10 @@
         <v>3557.7</v>
       </c>
       <c r="K9" t="n">
-        <v>3793.103448275862</v>
+        <v>3793.103448</v>
       </c>
       <c r="L9" t="n">
-        <v>606.8965517241377</v>
+        <v>606.896552</v>
       </c>
       <c r="M9" t="n">
         <v>4400</v>
@@ -870,6 +905,11 @@
       <c r="N9" t="n">
         <v>0</v>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -911,10 +951,10 @@
         <v>6186.02</v>
       </c>
       <c r="K10" t="n">
-        <v>6879.310344827587</v>
+        <v>6879.310345</v>
       </c>
       <c r="L10" t="n">
-        <v>1100.689655172413</v>
+        <v>1100.689655</v>
       </c>
       <c r="M10" t="n">
         <v>7980</v>
@@ -922,6 +962,11 @@
       <c r="N10" t="n">
         <v>0</v>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -963,10 +1008,10 @@
         <v>542.13</v>
       </c>
       <c r="K11" t="n">
-        <v>620.6896551724138</v>
+        <v>620.689655</v>
       </c>
       <c r="L11" t="n">
-        <v>99.31034482758616</v>
+        <v>99.310345</v>
       </c>
       <c r="M11" t="n">
         <v>720</v>
@@ -974,6 +1019,11 @@
       <c r="N11" t="n">
         <v>0</v>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1015,10 +1065,10 @@
         <v>1084.26</v>
       </c>
       <c r="K12" t="n">
-        <v>1241.379310344828</v>
+        <v>1241.37931</v>
       </c>
       <c r="L12" t="n">
-        <v>198.6206896551723</v>
+        <v>198.62069</v>
       </c>
       <c r="M12" t="n">
         <v>1440</v>
@@ -1026,6 +1076,11 @@
       <c r="N12" t="n">
         <v>0</v>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1067,10 +1122,10 @@
         <v>2076.12</v>
       </c>
       <c r="K13" t="n">
-        <v>2379.310344827587</v>
+        <v>2379.310345</v>
       </c>
       <c r="L13" t="n">
-        <v>380.6896551724135</v>
+        <v>380.689655</v>
       </c>
       <c r="M13" t="n">
         <v>2760</v>
@@ -1078,6 +1133,11 @@
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1119,10 +1179,10 @@
         <v>3329.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3793.103448275862</v>
+        <v>3793.103448</v>
       </c>
       <c r="L14" t="n">
-        <v>606.8965517241377</v>
+        <v>606.896552</v>
       </c>
       <c r="M14" t="n">
         <v>4400</v>
@@ -1130,6 +1190,11 @@
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1171,10 +1236,10 @@
         <v>4752</v>
       </c>
       <c r="K15" t="n">
-        <v>5431.034482758621</v>
+        <v>5431.034483</v>
       </c>
       <c r="L15" t="n">
-        <v>868.9655172413786</v>
+        <v>868.965517</v>
       </c>
       <c r="M15" t="n">
         <v>6300</v>
@@ -1182,6 +1247,11 @@
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1223,10 +1293,10 @@
         <v>6029</v>
       </c>
       <c r="K16" t="n">
-        <v>6896.551724137931</v>
+        <v>6896.551724</v>
       </c>
       <c r="L16" t="n">
-        <v>1103.448275862069</v>
+        <v>1103.448276</v>
       </c>
       <c r="M16" t="n">
         <v>8000</v>
@@ -1234,6 +1304,11 @@
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1275,10 +1350,10 @@
         <v>537.29</v>
       </c>
       <c r="K17" t="n">
-        <v>465.5172413793103</v>
+        <v>465.517241</v>
       </c>
       <c r="L17" t="n">
-        <v>74.48275862068965</v>
+        <v>74.482759</v>
       </c>
       <c r="M17" t="n">
         <v>540</v>
@@ -1286,6 +1361,11 @@
       <c r="N17" t="n">
         <v>0</v>
       </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1327,10 +1407,10 @@
         <v>2927</v>
       </c>
       <c r="K18" t="n">
-        <v>3275.862068965518</v>
+        <v>3275.862069</v>
       </c>
       <c r="L18" t="n">
-        <v>524.1379310344823</v>
+        <v>524.137931</v>
       </c>
       <c r="M18" t="n">
         <v>3800</v>
@@ -1338,6 +1418,11 @@
       <c r="N18" t="n">
         <v>0</v>
       </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1379,10 +1464,10 @@
         <v>5533.91</v>
       </c>
       <c r="K19" t="n">
-        <v>6387.068965517242</v>
+        <v>6387.068966</v>
       </c>
       <c r="L19" t="n">
-        <v>1021.931034482758</v>
+        <v>1021.931034</v>
       </c>
       <c r="M19" t="n">
         <v>7409</v>
@@ -1390,6 +1475,11 @@
       <c r="N19" t="n">
         <v>0</v>
       </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1431,10 +1521,10 @@
         <v>522.86</v>
       </c>
       <c r="K20" t="n">
-        <v>551.7241379310345</v>
+        <v>551.724138</v>
       </c>
       <c r="L20" t="n">
-        <v>88.27586206896547</v>
+        <v>88.275862</v>
       </c>
       <c r="M20" t="n">
         <v>640</v>
@@ -1442,6 +1532,11 @@
       <c r="N20" t="n">
         <v>0</v>
       </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1483,10 +1578,10 @@
         <v>2608.4</v>
       </c>
       <c r="K21" t="n">
-        <v>2751.724137931035</v>
+        <v>2751.724138</v>
       </c>
       <c r="L21" t="n">
-        <v>440.2758620689651</v>
+        <v>440.275862</v>
       </c>
       <c r="M21" t="n">
         <v>3192</v>
@@ -1494,6 +1589,11 @@
       <c r="N21" t="n">
         <v>0</v>
       </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1535,10 +1635,10 @@
         <v>4731.74</v>
       </c>
       <c r="K22" t="n">
-        <v>5044.827586206897</v>
+        <v>5044.827586</v>
       </c>
       <c r="L22" t="n">
-        <v>807.1724137931033</v>
+        <v>807.172414</v>
       </c>
       <c r="M22" t="n">
         <v>5852</v>
@@ -1546,6 +1646,11 @@
       <c r="N22" t="n">
         <v>0</v>
       </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1587,10 +1692,10 @@
         <v>7813.92</v>
       </c>
       <c r="K23" t="n">
-        <v>8689.655172413793</v>
+        <v>8689.655172000001</v>
       </c>
       <c r="L23" t="n">
-        <v>1390.344827586207</v>
+        <v>1390.344828</v>
       </c>
       <c r="M23" t="n">
         <v>10080</v>
@@ -1598,6 +1703,11 @@
       <c r="N23" t="n">
         <v>0</v>
       </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1636,19 +1746,24 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>422.11</v>
       </c>
       <c r="K24" t="n">
-        <v>396.551724137931</v>
+        <v>396.551724</v>
       </c>
       <c r="L24" t="n">
-        <v>63.44827586206896</v>
+        <v>63.448276</v>
       </c>
       <c r="M24" t="n">
-        <v>459.9999999999999</v>
+        <v>460</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1688,19 +1803,24 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1975.1</v>
       </c>
       <c r="K25" t="n">
-        <v>1801.724137931035</v>
+        <v>1939.655172</v>
       </c>
       <c r="L25" t="n">
-        <v>288.2758620689656</v>
+        <v>310.344828</v>
       </c>
       <c r="M25" t="n">
-        <v>2090.000000000001</v>
+        <v>2250</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1740,19 +1860,24 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>3828</v>
       </c>
       <c r="K26" t="n">
-        <v>3603.448275862069</v>
+        <v>3793.103448</v>
       </c>
       <c r="L26" t="n">
-        <v>576.551724137931</v>
+        <v>606.896552</v>
       </c>
       <c r="M26" t="n">
-        <v>4180</v>
+        <v>4400</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1792,19 +1917,24 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>7381.8</v>
       </c>
       <c r="K27" t="n">
-        <v>7112.068965517242</v>
+        <v>7413.793103</v>
       </c>
       <c r="L27" t="n">
-        <v>1137.931034482759</v>
+        <v>1186.206897</v>
       </c>
       <c r="M27" t="n">
-        <v>8250</v>
+        <v>8600</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Resina</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1844,19 +1974,24 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>66.64</v>
       </c>
       <c r="K28" t="n">
-        <v>64.65517241379311</v>
+        <v>68.96551700000001</v>
       </c>
       <c r="L28" t="n">
-        <v>10.34482758620689</v>
+        <v>11.034483</v>
       </c>
       <c r="M28" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1896,19 +2031,24 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>99.25</v>
       </c>
       <c r="K29" t="n">
-        <v>96.55172413793105</v>
+        <v>103.448276</v>
       </c>
       <c r="L29" t="n">
-        <v>15.44827586206895</v>
+        <v>16.551724</v>
       </c>
       <c r="M29" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1948,19 +2088,24 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>231.76</v>
       </c>
       <c r="K30" t="n">
-        <v>232.7586206896552</v>
+        <v>241.37931</v>
       </c>
       <c r="L30" t="n">
-        <v>37.24137931034483</v>
+        <v>38.62069</v>
       </c>
       <c r="M30" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2000,19 +2145,24 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>444.35</v>
       </c>
       <c r="K31" t="n">
-        <v>448.2758620689655</v>
+        <v>465.517241</v>
       </c>
       <c r="L31" t="n">
-        <v>71.72413793103448</v>
+        <v>74.482759</v>
       </c>
       <c r="M31" t="n">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2052,19 +2202,24 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>666.13</v>
       </c>
       <c r="K32" t="n">
-        <v>724.1379310344828</v>
+        <v>741.37931</v>
       </c>
       <c r="L32" t="n">
-        <v>115.8620689655172</v>
+        <v>118.62069</v>
       </c>
       <c r="M32" t="n">
-        <v>840</v>
+        <v>860</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -2107,10 +2262,10 @@
         <v>19.55</v>
       </c>
       <c r="K33" t="n">
-        <v>21.55172413793104</v>
+        <v>21.551724</v>
       </c>
       <c r="L33" t="n">
-        <v>3.448275862068964</v>
+        <v>3.448276</v>
       </c>
       <c r="M33" t="n">
         <v>25</v>
@@ -2118,6 +2273,11 @@
       <c r="N33" t="n">
         <v>0</v>
       </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2159,10 +2319,10 @@
         <v>53.77</v>
       </c>
       <c r="K34" t="n">
-        <v>56.03448275862069</v>
+        <v>56.034483</v>
       </c>
       <c r="L34" t="n">
-        <v>8.96551724137931</v>
+        <v>8.965517</v>
       </c>
       <c r="M34" t="n">
         <v>65</v>
@@ -2170,6 +2330,11 @@
       <c r="N34" t="n">
         <v>0</v>
       </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2211,10 +2376,10 @@
         <v>91.91</v>
       </c>
       <c r="K35" t="n">
-        <v>94.82758620689656</v>
+        <v>94.827586</v>
       </c>
       <c r="L35" t="n">
-        <v>15.17241379310344</v>
+        <v>15.172414</v>
       </c>
       <c r="M35" t="n">
         <v>110</v>
@@ -2222,6 +2387,11 @@
       <c r="N35" t="n">
         <v>0</v>
       </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2263,10 +2433,10 @@
         <v>161.33</v>
       </c>
       <c r="K36" t="n">
-        <v>163.7931034482759</v>
+        <v>163.793103</v>
       </c>
       <c r="L36" t="n">
-        <v>26.20689655172413</v>
+        <v>26.206897</v>
       </c>
       <c r="M36" t="n">
         <v>190</v>
@@ -2274,6 +2444,11 @@
       <c r="N36" t="n">
         <v>0</v>
       </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2315,10 +2490,10 @@
         <v>248.12</v>
       </c>
       <c r="K37" t="n">
-        <v>275.8620689655173</v>
+        <v>275.862069</v>
       </c>
       <c r="L37" t="n">
-        <v>44.13793103448273</v>
+        <v>44.137931</v>
       </c>
       <c r="M37" t="n">
         <v>320</v>
@@ -2326,6 +2501,11 @@
       <c r="N37" t="n">
         <v>0</v>
       </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2367,10 +2547,10 @@
         <v>427.79</v>
       </c>
       <c r="K38" t="n">
-        <v>474.1379310344828</v>
+        <v>474.137931</v>
       </c>
       <c r="L38" t="n">
-        <v>75.86206896551721</v>
+        <v>75.86206900000001</v>
       </c>
       <c r="M38" t="n">
         <v>550</v>
@@ -2378,6 +2558,11 @@
       <c r="N38" t="n">
         <v>0</v>
       </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2419,10 +2604,10 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>237.0689655172414</v>
+        <v>237.068966</v>
       </c>
       <c r="L39" t="n">
-        <v>37.93103448275863</v>
+        <v>37.931034</v>
       </c>
       <c r="M39" t="n">
         <v>275</v>
@@ -2430,6 +2615,11 @@
       <c r="N39" t="n">
         <v>0</v>
       </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2471,10 +2661,10 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>543.1034482758621</v>
+        <v>543.103448</v>
       </c>
       <c r="L40" t="n">
-        <v>86.89655172413794</v>
+        <v>86.896552</v>
       </c>
       <c r="M40" t="n">
         <v>630</v>
@@ -2482,6 +2672,11 @@
       <c r="N40" t="n">
         <v>0</v>
       </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2523,10 +2718,10 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>948.2758620689656</v>
+        <v>948.275862</v>
       </c>
       <c r="L41" t="n">
-        <v>151.7241379310345</v>
+        <v>151.724138</v>
       </c>
       <c r="M41" t="n">
         <v>1100</v>
@@ -2534,6 +2729,11 @@
       <c r="N41" t="n">
         <v>0</v>
       </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2572,13 +2772,13 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>93.87</v>
       </c>
       <c r="K42" t="n">
-        <v>91.37931034482759</v>
+        <v>91.37931</v>
       </c>
       <c r="L42" t="n">
-        <v>14.62068965517241</v>
+        <v>14.62069</v>
       </c>
       <c r="M42" t="n">
         <v>106</v>
@@ -2586,6 +2786,11 @@
       <c r="N42" t="n">
         <v>0</v>
       </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2624,13 +2829,13 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>279.27</v>
       </c>
       <c r="K43" t="n">
-        <v>268.9655172413793</v>
+        <v>268.965517</v>
       </c>
       <c r="L43" t="n">
-        <v>43.03448275862069</v>
+        <v>43.034483</v>
       </c>
       <c r="M43" t="n">
         <v>312</v>
@@ -2638,6 +2843,11 @@
       <c r="N43" t="n">
         <v>0</v>
       </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2676,13 +2886,13 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>413.56</v>
       </c>
       <c r="K44" t="n">
-        <v>401.7241379310345</v>
+        <v>401.724138</v>
       </c>
       <c r="L44" t="n">
-        <v>64.27586206896552</v>
+        <v>64.275862</v>
       </c>
       <c r="M44" t="n">
         <v>466</v>
@@ -2690,6 +2900,11 @@
       <c r="N44" t="n">
         <v>0</v>
       </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2728,13 +2943,13 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>747.41</v>
       </c>
       <c r="K45" t="n">
-        <v>727.5862068965517</v>
+        <v>727.5862069999999</v>
       </c>
       <c r="L45" t="n">
-        <v>116.4137931034483</v>
+        <v>116.413793</v>
       </c>
       <c r="M45" t="n">
         <v>844</v>
@@ -2742,6 +2957,11 @@
       <c r="N45" t="n">
         <v>0</v>
       </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2780,13 +3000,13 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1323.21</v>
       </c>
       <c r="K46" t="n">
-        <v>1296.551724137931</v>
+        <v>1296.551724</v>
       </c>
       <c r="L46" t="n">
-        <v>207.448275862069</v>
+        <v>207.448276</v>
       </c>
       <c r="M46" t="n">
         <v>1504</v>
@@ -2794,6 +3014,11 @@
       <c r="N46" t="n">
         <v>0</v>
       </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2835,10 +3060,10 @@
         <v>421.06</v>
       </c>
       <c r="K47" t="n">
-        <v>431.0344827586207</v>
+        <v>431.034483</v>
       </c>
       <c r="L47" t="n">
-        <v>68.9655172413793</v>
+        <v>68.96551700000001</v>
       </c>
       <c r="M47" t="n">
         <v>500</v>
@@ -2846,6 +3071,11 @@
       <c r="N47" t="n">
         <v>0</v>
       </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2887,10 +3117,10 @@
         <v>182.7</v>
       </c>
       <c r="K48" t="n">
-        <v>176.7241379310345</v>
+        <v>176.724138</v>
       </c>
       <c r="L48" t="n">
-        <v>28.27586206896549</v>
+        <v>28.275862</v>
       </c>
       <c r="M48" t="n">
         <v>205</v>
@@ -2898,6 +3128,11 @@
       <c r="N48" t="n">
         <v>0</v>
       </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2939,10 +3174,10 @@
         <v>182.7</v>
       </c>
       <c r="K49" t="n">
-        <v>172.4137931034483</v>
+        <v>172.413793</v>
       </c>
       <c r="L49" t="n">
-        <v>27.58620689655172</v>
+        <v>27.586207</v>
       </c>
       <c r="M49" t="n">
         <v>200</v>
@@ -2950,6 +3185,11 @@
       <c r="N49" t="n">
         <v>0</v>
       </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2959,7 +3199,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">EPOXY-HOJUELA (combinación) </t>
+          <t>EPOXY-HOJUELA (combinación)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2991,10 +3231,10 @@
         <v>214.5</v>
       </c>
       <c r="K50" t="n">
-        <v>202.5862068965517</v>
+        <v>202.586207</v>
       </c>
       <c r="L50" t="n">
-        <v>32.41379310344826</v>
+        <v>32.413793</v>
       </c>
       <c r="M50" t="n">
         <v>235</v>
@@ -3002,6 +3242,11 @@
       <c r="N50" t="n">
         <v>0</v>
       </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3011,7 +3256,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">EPOXY-HOJUELA (combinación) </t>
+          <t>EPOXY-HOJUELA (combinación)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3043,10 +3288,10 @@
         <v>214.5</v>
       </c>
       <c r="K51" t="n">
-        <v>198.2758620689655</v>
+        <v>198.275862</v>
       </c>
       <c r="L51" t="n">
-        <v>31.72413793103448</v>
+        <v>31.724138</v>
       </c>
       <c r="M51" t="n">
         <v>230</v>
@@ -3054,6 +3299,11 @@
       <c r="N51" t="n">
         <v>0</v>
       </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3095,10 +3345,10 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>56.03448275862069</v>
+        <v>56.034483</v>
       </c>
       <c r="L52" t="n">
-        <v>8.965517241379311</v>
+        <v>8.965517</v>
       </c>
       <c r="M52" t="n">
         <v>65</v>
@@ -3106,6 +3356,11 @@
       <c r="N52" t="n">
         <v>0</v>
       </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3147,10 +3402,10 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>47.41379310344828</v>
+        <v>47.413793</v>
       </c>
       <c r="L53" t="n">
-        <v>7.586206896551724</v>
+        <v>7.586207</v>
       </c>
       <c r="M53" t="n">
         <v>55</v>
@@ -3158,6 +3413,11 @@
       <c r="N53" t="n">
         <v>0</v>
       </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3199,10 +3459,10 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>77.58620689655173</v>
+        <v>77.586207</v>
       </c>
       <c r="L54" t="n">
-        <v>12.41379310344828</v>
+        <v>12.413793</v>
       </c>
       <c r="M54" t="n">
         <v>90</v>
@@ -3210,6 +3470,11 @@
       <c r="N54" t="n">
         <v>0</v>
       </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3251,10 +3516,10 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>60.3448275862069</v>
+        <v>60.344828</v>
       </c>
       <c r="L55" t="n">
-        <v>9.655172413793103</v>
+        <v>9.655172</v>
       </c>
       <c r="M55" t="n">
         <v>70</v>
@@ -3262,6 +3527,11 @@
       <c r="N55" t="n">
         <v>0</v>
       </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3303,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>405.1724137931035</v>
+        <v>405.172414</v>
       </c>
       <c r="L56" t="n">
-        <v>64.82758620689656</v>
+        <v>64.827586</v>
       </c>
       <c r="M56" t="n">
         <v>470.0000000000001</v>
@@ -3314,6 +3584,11 @@
       <c r="N56" t="n">
         <v>0</v>
       </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3355,10 +3630,10 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>715.5172413793103</v>
+        <v>715.517241</v>
       </c>
       <c r="L57" t="n">
-        <v>114.4827586206897</v>
+        <v>114.482759</v>
       </c>
       <c r="M57" t="n">
         <v>830</v>
@@ -3366,6 +3641,11 @@
       <c r="N57" t="n">
         <v>0</v>
       </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3407,10 +3687,10 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>426.7241379310345</v>
+        <v>426.724138</v>
       </c>
       <c r="L58" t="n">
-        <v>68.27586206896552</v>
+        <v>68.275862</v>
       </c>
       <c r="M58" t="n">
         <v>495</v>
@@ -3418,6 +3698,11 @@
       <c r="N58" t="n">
         <v>0</v>
       </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3459,10 +3744,10 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>737.0689655172414</v>
+        <v>737.068966</v>
       </c>
       <c r="L59" t="n">
-        <v>117.9310344827586</v>
+        <v>117.931034</v>
       </c>
       <c r="M59" t="n">
         <v>855</v>
@@ -3470,6 +3755,11 @@
       <c r="N59" t="n">
         <v>0</v>
       </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3482,8 +3772,10 @@
           <t>EPO-PAINT (A y B)</t>
         </is>
       </c>
-      <c r="C60" t="n">
-        <v>0</v>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="D60" t="n">
         <v>5</v>
@@ -3520,6 +3812,11 @@
       <c r="N60" t="n">
         <v>0</v>
       </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3532,8 +3829,10 @@
           <t>ARENA SILICA</t>
         </is>
       </c>
-      <c r="C61" t="n">
-        <v>0</v>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="D61" t="n">
         <v>5</v>
@@ -3570,6 +3869,11 @@
       <c r="N61" t="n">
         <v>0</v>
       </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3611,10 +3915,10 @@
         <v>474.06</v>
       </c>
       <c r="K62" t="n">
-        <v>426.7241379310345</v>
+        <v>426.724138</v>
       </c>
       <c r="L62" t="n">
-        <v>68.27586206896547</v>
+        <v>68.275862</v>
       </c>
       <c r="M62" t="n">
         <v>495</v>
@@ -3622,6 +3926,11 @@
       <c r="N62" t="n">
         <v>0</v>
       </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Herramienta</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3663,16 +3972,21 @@
         <v>406.09</v>
       </c>
       <c r="K63" t="n">
-        <v>366.3793103448277</v>
+        <v>366.37931</v>
       </c>
       <c r="L63" t="n">
-        <v>58.62068965517238</v>
+        <v>58.62069</v>
       </c>
       <c r="M63" t="n">
-        <v>425.0000000000001</v>
+        <v>425</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Herramienta</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -3715,16 +4029,21 @@
         <v>71.26000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>64.65517241379312</v>
+        <v>64.65517199999999</v>
       </c>
       <c r="L64" t="n">
-        <v>10.34482758620689</v>
+        <v>10.344828</v>
       </c>
       <c r="M64" t="n">
-        <v>75.00000000000001</v>
+        <v>75</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Herramienta</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -3767,10 +4086,10 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>1370.689655172414</v>
+        <v>1370.689655</v>
       </c>
       <c r="L65" t="n">
-        <v>219.3103448275862</v>
+        <v>219.310345</v>
       </c>
       <c r="M65" t="n">
         <v>1590</v>
@@ -3778,6 +4097,11 @@
       <c r="N65" t="n">
         <v>0</v>
       </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Herramienta</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3819,16 +4143,21 @@
         <v>370.51</v>
       </c>
       <c r="K66" t="n">
-        <v>336.2068965517242</v>
+        <v>336.206897</v>
       </c>
       <c r="L66" t="n">
-        <v>53.79310344827587</v>
+        <v>53.793103</v>
       </c>
       <c r="M66" t="n">
-        <v>390.0000000000001</v>
+        <v>390</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Herramienta</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -3871,10 +4200,10 @@
         <v>62.71</v>
       </c>
       <c r="K67" t="n">
-        <v>56.03448275862069</v>
+        <v>56.034483</v>
       </c>
       <c r="L67" t="n">
-        <v>8.96551724137931</v>
+        <v>8.965517</v>
       </c>
       <c r="M67" t="n">
         <v>65</v>
@@ -3882,6 +4211,11 @@
       <c r="N67" t="n">
         <v>0</v>
       </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Herramienta</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3923,10 +4257,10 @@
         <v>77.92</v>
       </c>
       <c r="K68" t="n">
-        <v>68.96551724137932</v>
+        <v>68.96551700000001</v>
       </c>
       <c r="L68" t="n">
-        <v>11.03448275862068</v>
+        <v>11.034483</v>
       </c>
       <c r="M68" t="n">
         <v>80</v>
@@ -3934,6 +4268,11 @@
       <c r="N68" t="n">
         <v>0</v>
       </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Herramienta</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3975,16 +4314,21 @@
         <v>193.32</v>
       </c>
       <c r="K69" t="n">
-        <v>172.4137931034484</v>
+        <v>172.413793</v>
       </c>
       <c r="L69" t="n">
-        <v>27.58620689655172</v>
+        <v>27.586207</v>
       </c>
       <c r="M69" t="n">
-        <v>200.0000000000001</v>
+        <v>200</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Herramienta</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -4027,10 +4371,10 @@
         <v>38.01</v>
       </c>
       <c r="K70" t="n">
-        <v>34.48275862068966</v>
+        <v>34.482759</v>
       </c>
       <c r="L70" t="n">
-        <v>5.517241379310342</v>
+        <v>5.517241</v>
       </c>
       <c r="M70" t="n">
         <v>40</v>
@@ -4038,6 +4382,11 @@
       <c r="N70" t="n">
         <v>0</v>
       </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Herramienta</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4079,10 +4428,10 @@
         <v>133.02</v>
       </c>
       <c r="K71" t="n">
-        <v>120.6896551724138</v>
+        <v>120.689655</v>
       </c>
       <c r="L71" t="n">
-        <v>19.31034482758619</v>
+        <v>19.310345</v>
       </c>
       <c r="M71" t="n">
         <v>140</v>
@@ -4090,6 +4439,11 @@
       <c r="N71" t="n">
         <v>0</v>
       </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Herramienta</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4131,10 +4485,10 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>163.7931034482759</v>
+        <v>163.793103</v>
       </c>
       <c r="L72" t="n">
-        <v>26.20689655172415</v>
+        <v>26.206897</v>
       </c>
       <c r="M72" t="n">
         <v>190.0000000000001</v>
@@ -4142,6 +4496,11 @@
       <c r="N72" t="n">
         <v>0</v>
       </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Herramienta</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4183,10 +4542,10 @@
         <v>660.26</v>
       </c>
       <c r="K73" t="n">
-        <v>599.1379310344828</v>
+        <v>599.137931</v>
       </c>
       <c r="L73" t="n">
-        <v>95.86206896551721</v>
+        <v>95.86206900000001</v>
       </c>
       <c r="M73" t="n">
         <v>695</v>
@@ -4194,6 +4553,11 @@
       <c r="N73" t="n">
         <v>0</v>
       </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Herramienta</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4235,10 +4599,10 @@
         <v>418</v>
       </c>
       <c r="K74" t="n">
-        <v>379.3103448275862</v>
+        <v>379.310345</v>
       </c>
       <c r="L74" t="n">
-        <v>60.68965517241378</v>
+        <v>60.689655</v>
       </c>
       <c r="M74" t="n">
         <v>440</v>
@@ -4246,6 +4610,11 @@
       <c r="N74" t="n">
         <v>0</v>
       </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Herramienta</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4287,10 +4656,10 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>1650.862068965517</v>
+        <v>1650.862069</v>
       </c>
       <c r="L75" t="n">
-        <v>264.1379310344827</v>
+        <v>264.137931</v>
       </c>
       <c r="M75" t="n">
         <v>1915</v>
@@ -4298,6 +4667,11 @@
       <c r="N75" t="n">
         <v>0</v>
       </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Herramienta</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4339,10 +4713,10 @@
         <v>74.81</v>
       </c>
       <c r="K76" t="n">
-        <v>77.58620689655173</v>
+        <v>77.586207</v>
       </c>
       <c r="L76" t="n">
-        <v>12.41379310344827</v>
+        <v>12.413793</v>
       </c>
       <c r="M76" t="n">
         <v>90</v>
@@ -4350,6 +4724,11 @@
       <c r="N76" t="n">
         <v>0</v>
       </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Herramienta</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4391,10 +4770,10 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>215.5172413793103</v>
+        <v>215.517241</v>
       </c>
       <c r="L77" t="n">
-        <v>34.48275862068964</v>
+        <v>34.482759</v>
       </c>
       <c r="M77" t="n">
         <v>249.9999999999999</v>
@@ -4402,6 +4781,11 @@
       <c r="N77" t="n">
         <v>0</v>
       </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Herramienta</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4443,10 +4827,10 @@
         <v>3452.64</v>
       </c>
       <c r="K78" t="n">
-        <v>3447.413793103448</v>
+        <v>3447.413793</v>
       </c>
       <c r="L78" t="n">
-        <v>551.5862068965516</v>
+        <v>551.5862069999999</v>
       </c>
       <c r="M78" t="n">
         <v>3999</v>
@@ -4454,6 +4838,11 @@
       <c r="N78" t="n">
         <v>0</v>
       </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Herramienta</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4495,10 +4884,10 @@
         <v>444.45</v>
       </c>
       <c r="K79" t="n">
-        <v>500.0000000000001</v>
+        <v>500</v>
       </c>
       <c r="L79" t="n">
-        <v>79.99999999999994</v>
+        <v>80</v>
       </c>
       <c r="M79" t="n">
         <v>580</v>
@@ -4506,6 +4895,11 @@
       <c r="N79" t="n">
         <v>0</v>
       </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Acabado</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4547,10 +4941,10 @@
         <v>433.74</v>
       </c>
       <c r="K80" t="n">
-        <v>482.7586206896552</v>
+        <v>482.758621</v>
       </c>
       <c r="L80" t="n">
-        <v>77.24137931034477</v>
+        <v>77.24137899999999</v>
       </c>
       <c r="M80" t="n">
         <v>560</v>
@@ -4558,6 +4952,11 @@
       <c r="N80" t="n">
         <v>0</v>
       </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Acabado</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4599,10 +4998,10 @@
         <v>423.54</v>
       </c>
       <c r="K81" t="n">
-        <v>465.5172413793103</v>
+        <v>465.517241</v>
       </c>
       <c r="L81" t="n">
-        <v>74.48275862068965</v>
+        <v>74.482759</v>
       </c>
       <c r="M81" t="n">
         <v>540</v>
@@ -4610,6 +5009,11 @@
       <c r="N81" t="n">
         <v>0</v>
       </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Acabado</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4651,10 +5055,10 @@
         <v>413.8</v>
       </c>
       <c r="K82" t="n">
-        <v>448.2758620689655</v>
+        <v>448.275862</v>
       </c>
       <c r="L82" t="n">
-        <v>71.72413793103448</v>
+        <v>71.724138</v>
       </c>
       <c r="M82" t="n">
         <v>520</v>
@@ -4662,6 +5066,11 @@
       <c r="N82" t="n">
         <v>0</v>
       </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Acabado</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4703,10 +5112,10 @@
         <v>400</v>
       </c>
       <c r="K83" t="n">
-        <v>413.7931034482759</v>
+        <v>413.793103</v>
       </c>
       <c r="L83" t="n">
-        <v>66.20689655172413</v>
+        <v>66.206897</v>
       </c>
       <c r="M83" t="n">
         <v>480</v>
@@ -4714,6 +5123,11 @@
       <c r="N83" t="n">
         <v>0</v>
       </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Acabado</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4752,19 +5166,24 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>380</v>
+        <v>1520</v>
       </c>
       <c r="K84" t="n">
-        <v>396.551724137931</v>
+        <v>1586.206897</v>
       </c>
       <c r="L84" t="n">
-        <v>63.44827586206895</v>
+        <v>253.793103</v>
       </c>
       <c r="M84" t="n">
-        <v>460</v>
+        <v>1840</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Acabado</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -4804,19 +5223,24 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>361</v>
+        <v>6859</v>
       </c>
       <c r="K85" t="n">
-        <v>379.3103448275862</v>
+        <v>7206.896552</v>
       </c>
       <c r="L85" t="n">
-        <v>60.68965517241378</v>
+        <v>1153.103448</v>
       </c>
       <c r="M85" t="n">
-        <v>440</v>
+        <v>8360</v>
       </c>
       <c r="N85" t="n">
         <v>0</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Acabado</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -4856,19 +5280,24 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>231.58</v>
+        <v>926.3200000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>237.0689655172414</v>
+        <v>948.275862</v>
       </c>
       <c r="L86" t="n">
-        <v>37.93103448275861</v>
+        <v>151.724138</v>
       </c>
       <c r="M86" t="n">
-        <v>275</v>
+        <v>1100</v>
       </c>
       <c r="N86" t="n">
         <v>0</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Acabado</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -4908,19 +5337,24 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>182.83</v>
+        <v>3473.77</v>
       </c>
       <c r="K87" t="n">
-        <v>193.9655172413793</v>
+        <v>3685.344828</v>
       </c>
       <c r="L87" t="n">
-        <v>31.03448275862067</v>
+        <v>589.655172</v>
       </c>
       <c r="M87" t="n">
-        <v>225</v>
+        <v>4275</v>
       </c>
       <c r="N87" t="n">
         <v>0</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Acabado</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -4963,10 +5397,10 @@
         <v>29.34</v>
       </c>
       <c r="K88" t="n">
-        <v>30.17241379310345</v>
+        <v>30.172414</v>
       </c>
       <c r="L88" t="n">
-        <v>4.827586206896548</v>
+        <v>4.827586</v>
       </c>
       <c r="M88" t="n">
         <v>35</v>
@@ -4974,6 +5408,11 @@
       <c r="N88" t="n">
         <v>0</v>
       </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5015,10 +5454,10 @@
         <v>29.34</v>
       </c>
       <c r="K89" t="n">
-        <v>25.86206896551724</v>
+        <v>25.862069</v>
       </c>
       <c r="L89" t="n">
-        <v>4.137931034482758</v>
+        <v>4.137931</v>
       </c>
       <c r="M89" t="n">
         <v>30</v>
@@ -5026,6 +5465,11 @@
       <c r="N89" t="n">
         <v>0</v>
       </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5067,16 +5511,21 @@
         <v>2373.11</v>
       </c>
       <c r="K90" t="n">
-        <v>2153.448275862069</v>
+        <v>2153.448276</v>
       </c>
       <c r="L90" t="n">
-        <v>344.5517241379307</v>
+        <v>344.551724</v>
       </c>
       <c r="M90" t="n">
         <v>2498</v>
       </c>
       <c r="N90" t="n">
         <v>0</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Herramienta</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5153,7 +5602,7 @@
         </is>
       </c>
       <c r="B9">
-        <f>VLOOKUP(B6, Cat_Productos!$A$2:$G$46, 5, FALSE)</f>
+        <f>VLOOKUP(B6, Cat_Productos!$A$2:$G$58, 5, FALSE)</f>
         <v/>
       </c>
     </row>
@@ -5217,7 +5666,7 @@
         <v>1.5</v>
       </c>
       <c r="B15" s="2">
-        <f>IFERROR(SUMIFS(Cat_Productos!$D$2:$D$46, Cat_Productos!$A$2:$A$46, $B$6, Cat_Productos!$C$2:$C$46, A15), 0)</f>
+        <f>IFERROR(SUMIFS(Cat_Productos!$D$2:$D$58, Cat_Productos!$A$2:$A$58, $B$6, Cat_Productos!$C$2:$C$58, A15), 0)</f>
         <v/>
       </c>
       <c r="C15" s="3">
@@ -5241,7 +5690,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="2">
-        <f>IFERROR(SUMIFS(Cat_Productos!$D$2:$D$46, Cat_Productos!$A$2:$A$46, $B$6, Cat_Productos!$C$2:$C$46, A16), 0)</f>
+        <f>IFERROR(SUMIFS(Cat_Productos!$D$2:$D$58, Cat_Productos!$A$2:$A$58, $B$6, Cat_Productos!$C$2:$C$58, A16), 0)</f>
         <v/>
       </c>
       <c r="C16" s="3">
@@ -5265,7 +5714,7 @@
         <v>6</v>
       </c>
       <c r="B17" s="2">
-        <f>IFERROR(SUMIFS(Cat_Productos!$D$2:$D$46, Cat_Productos!$A$2:$A$46, $B$6, Cat_Productos!$C$2:$C$46, A17), 0)</f>
+        <f>IFERROR(SUMIFS(Cat_Productos!$D$2:$D$58, Cat_Productos!$A$2:$A$58, $B$6, Cat_Productos!$C$2:$C$58, A17), 0)</f>
         <v/>
       </c>
       <c r="C17" s="3">
@@ -5289,7 +5738,7 @@
         <v>10</v>
       </c>
       <c r="B18" s="2">
-        <f>IFERROR(SUMIFS(Cat_Productos!$D$2:$D$46, Cat_Productos!$A$2:$A$46, $B$6, Cat_Productos!$C$2:$C$46, A18), 0)</f>
+        <f>IFERROR(SUMIFS(Cat_Productos!$D$2:$D$58, Cat_Productos!$A$2:$A$58, $B$6, Cat_Productos!$C$2:$C$58, A18), 0)</f>
         <v/>
       </c>
       <c r="C18" s="3">
@@ -5313,7 +5762,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <f>IFERROR(SUMIFS(Cat_Productos!$D$2:$D$46, Cat_Productos!$A$2:$A$46, $B$6, Cat_Productos!$C$2:$C$46, A19), 0)</f>
+        <f>IFERROR(SUMIFS(Cat_Productos!$D$2:$D$58, Cat_Productos!$A$2:$A$58, $B$6, Cat_Productos!$C$2:$C$58, A19), 0)</f>
         <v/>
       </c>
       <c r="C19" s="3">
@@ -5337,7 +5786,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2">
-        <f>IFERROR(SUMIFS(Cat_Productos!$D$2:$D$46, Cat_Productos!$A$2:$A$46, $B$6, Cat_Productos!$C$2:$C$46, A20), 0)</f>
+        <f>IFERROR(SUMIFS(Cat_Productos!$D$2:$D$58, Cat_Productos!$A$2:$A$58, $B$6, Cat_Productos!$C$2:$C$58, A20), 0)</f>
         <v/>
       </c>
       <c r="C20" s="3">
@@ -5425,7 +5874,7 @@
         </is>
       </c>
       <c r="C27">
-        <f>B11 * (100 / (100 + IFERROR(SUMIFS(Cat_Productos!$G$2:$G$46, Cat_Productos!$A$2:$A$46, $B$6), 50)))</f>
+        <f>B11 * (100 / (100 + IFERROR(SUMIFS(Cat_Productos!$G$2:$G$58, Cat_Productos!$A$2:$A$58, $B$6), 50)))</f>
         <v/>
       </c>
       <c r="D27" t="inlineStr">
@@ -5466,7 +5915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5475,6 +5924,11 @@
           <t>Producto</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
       <c r="C1" t="inlineStr">
         <is>
           <t>Presentacion</t>
@@ -5517,6 +5971,7 @@
           <t>EPOXY PISOS (A Y B) TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>1.5</v>
       </c>
@@ -5532,6 +5987,8 @@
       <c r="G2" t="n">
         <v>50</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5539,6 +5996,7 @@
           <t>EPOXY PISOS (A Y B) TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>3</v>
       </c>
@@ -5554,6 +6012,8 @@
       <c r="G3" t="n">
         <v>50</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5561,6 +6021,7 @@
           <t>EPOXY PISOS (A Y B) TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>6</v>
       </c>
@@ -5576,6 +6037,8 @@
       <c r="G4" t="n">
         <v>50</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5583,6 +6046,7 @@
           <t>EPOXY PISOS (A Y B) TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>10</v>
       </c>
@@ -5598,6 +6062,8 @@
       <c r="G5" t="n">
         <v>50</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5605,6 +6071,7 @@
           <t>EPOXY PISOS (A Y B) TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>15</v>
       </c>
@@ -5620,6 +6087,8 @@
       <c r="G6" t="n">
         <v>50</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5627,6 +6096,7 @@
           <t>EPOXY PISOS (A Y B) TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>20</v>
       </c>
@@ -5642,6 +6112,8 @@
       <c r="G7" t="n">
         <v>50</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5649,6 +6121,7 @@
           <t>EPO-FAST (A Y B) TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>2</v>
       </c>
@@ -5664,6 +6137,8 @@
       <c r="G8" t="n">
         <v>84</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5671,6 +6146,7 @@
           <t>EPO-FAST (A Y B) TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>6</v>
       </c>
@@ -5686,6 +6162,8 @@
       <c r="G9" t="n">
         <v>84</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5693,6 +6171,7 @@
           <t>EPO-FAST (A Y B) TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>10</v>
       </c>
@@ -5708,6 +6187,8 @@
       <c r="G10" t="n">
         <v>84</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5715,6 +6196,7 @@
           <t>EPO-FAST (A Y B) TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>19</v>
       </c>
@@ -5730,6 +6212,8 @@
       <c r="G11" t="n">
         <v>84</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5737,6 +6221,7 @@
           <t>EPO-DEEP TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>1.42</v>
       </c>
@@ -5752,6 +6237,8 @@
       <c r="G12" t="n">
         <v>42</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5759,6 +6246,7 @@
           <t>EPO-DEEP TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>4.26</v>
       </c>
@@ -5774,6 +6262,8 @@
       <c r="G13" t="n">
         <v>42</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5781,6 +6271,7 @@
           <t>EPO-DEEP TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>7.1</v>
       </c>
@@ -5796,6 +6287,8 @@
       <c r="G14" t="n">
         <v>42</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5803,6 +6296,7 @@
           <t>EPO-DEEP TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>17.04</v>
       </c>
@@ -5818,6 +6312,8 @@
       <c r="G15" t="n">
         <v>42</v>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5825,6 +6321,7 @@
           <t>EPOXY PRIMER (A Y B) TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>1.35</v>
       </c>
@@ -5840,6 +6337,8 @@
       <c r="G16" t="n">
         <v>35</v>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5847,6 +6346,7 @@
           <t>EPOXY PRIMER (A Y B) TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>10</v>
       </c>
@@ -5862,6 +6362,8 @@
       <c r="G17" t="n">
         <v>35</v>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5869,6 +6371,7 @@
           <t>EPOXY PRIMER (A Y B) TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>20.025</v>
       </c>
@@ -5884,6 +6387,8 @@
       <c r="G18" t="n">
         <v>35</v>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5891,6 +6396,7 @@
           <t>EPO-DEEP ULTRA (A Y B) TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>1.333</v>
       </c>
@@ -5906,6 +6412,8 @@
       <c r="G19" t="n">
         <v>33</v>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5913,6 +6421,7 @@
           <t>EPO-DEEP ULTRA (A Y B) TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>6.65</v>
       </c>
@@ -5928,6 +6437,8 @@
       <c r="G20" t="n">
         <v>33</v>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5935,6 +6446,7 @@
           <t>EPO-DEEP ULTRA (A Y B) TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>13.3</v>
       </c>
@@ -5950,6 +6462,8 @@
       <c r="G21" t="n">
         <v>33</v>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5957,6 +6471,7 @@
           <t>EPO-DEEP ULTRA (A Y B) TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>24</v>
       </c>
@@ -5972,6 +6487,8 @@
       <c r="G22" t="n">
         <v>33</v>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5979,6 +6496,7 @@
           <t>POLIURETANO (A Y B) TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>1</v>
       </c>
@@ -5994,6 +6512,8 @@
       <c r="G23" t="n">
         <v>50</v>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6001,6 +6521,7 @@
           <t>POLIURETANO (A Y B) TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>5</v>
       </c>
@@ -6016,6 +6537,8 @@
       <c r="G24" t="n">
         <v>50</v>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6023,6 +6546,7 @@
           <t>POLIURETANO (A Y B) TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>10</v>
       </c>
@@ -6038,6 +6562,8 @@
       <c r="G25" t="n">
         <v>50</v>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6045,6 +6571,7 @@
           <t>POLIURETANO (A Y B) TRANSPARENTE</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>20</v>
       </c>
@@ -6060,6 +6587,8 @@
       <c r="G26" t="n">
         <v>50</v>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6067,12 +6596,14 @@
           <t>EPOXY PASTA COLORES SÓLIDOS</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>60</v>
       </c>
       <c r="D27" t="n">
         <v>75</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
         <v>100</v>
       </c>
@@ -6094,12 +6625,14 @@
           <t>EPOXY PASTA COLORES SÓLIDOS</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>100</v>
       </c>
       <c r="D28" t="n">
         <v>112</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
         <v>100</v>
       </c>
@@ -6121,12 +6654,14 @@
           <t>EPOXY PASTA COLORES SÓLIDOS</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>250</v>
       </c>
       <c r="D29" t="n">
         <v>270</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
         <v>100</v>
       </c>
@@ -6148,12 +6683,14 @@
           <t>EPOXY PASTA COLORES SÓLIDOS</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>500</v>
       </c>
       <c r="D30" t="n">
         <v>520</v>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
         <v>100</v>
       </c>
@@ -6175,12 +6712,14 @@
           <t>EPOXY PASTA COLORES SÓLIDOS</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
         <v>840</v>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
         <v>100</v>
       </c>
@@ -6202,12 +6741,14 @@
           <t>EPOXY TINTA</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>20</v>
       </c>
       <c r="D32" t="n">
         <v>25</v>
       </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
         <v>100</v>
       </c>
@@ -6229,12 +6770,14 @@
           <t>EPOXY TINTA</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>60</v>
       </c>
       <c r="D33" t="n">
         <v>65</v>
       </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
         <v>100</v>
       </c>
@@ -6256,12 +6799,14 @@
           <t>EPOXY TINTA</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>100</v>
       </c>
       <c r="D34" t="n">
         <v>110</v>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
         <v>100</v>
       </c>
@@ -6283,12 +6828,14 @@
           <t>EPOXY TINTA</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>250</v>
       </c>
       <c r="D35" t="n">
         <v>190</v>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
         <v>100</v>
       </c>
@@ -6310,12 +6857,14 @@
           <t>EPOXY TINTA</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>500</v>
       </c>
       <c r="D36" t="n">
         <v>320</v>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
         <v>100</v>
       </c>
@@ -6337,12 +6886,14 @@
           <t>EPOXY TINTA</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
         <v>550</v>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
         <v>100</v>
       </c>
@@ -6364,12 +6915,14 @@
           <t>PIGMENTOS FOTOLUMINISCENTES</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>20</v>
       </c>
       <c r="D38" t="n">
         <v>275</v>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
         <v>100</v>
       </c>
@@ -6391,12 +6944,14 @@
           <t>PIGMENTOS FOTOLUMINISCENTES</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>50</v>
       </c>
       <c r="D39" t="n">
         <v>630</v>
       </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
         <v>100</v>
       </c>
@@ -6418,12 +6973,14 @@
           <t>PIGMENTOS FOTOLUMINISCENTES</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
         <v>100</v>
       </c>
       <c r="D40" t="n">
         <v>1100</v>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
         <v>100</v>
       </c>
@@ -6445,12 +7002,14 @@
           <t>EPOXY METAL PERLADO Y METÁLICOS EN POLVO</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
         <v>10</v>
       </c>
       <c r="D41" t="n">
         <v>106</v>
       </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
         <v>100</v>
       </c>
@@ -6472,12 +7031,14 @@
           <t>EPOXY METAL PERLADO Y METÁLICOS EN POLVO</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
         <v>30</v>
       </c>
       <c r="D42" t="n">
         <v>312</v>
       </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
         <v>100</v>
       </c>
@@ -6499,12 +7060,14 @@
           <t>EPOXY METAL PERLADO Y METÁLICOS EN POLVO</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
         <v>50</v>
       </c>
       <c r="D43" t="n">
         <v>466</v>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
         <v>100</v>
       </c>
@@ -6526,12 +7089,14 @@
           <t>EPOXY METAL PERLADO Y METÁLICOS EN POLVO</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
         <v>100</v>
       </c>
       <c r="D44" t="n">
         <v>844</v>
       </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="n">
         <v>100</v>
       </c>
@@ -6553,12 +7118,14 @@
           <t>EPOXY METAL PERLADO Y METÁLICOS EN POLVO</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
         <v>200</v>
       </c>
       <c r="D45" t="n">
         <v>1504</v>
       </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
         <v>100</v>
       </c>
@@ -6571,6 +7138,383 @@
       <c r="I45" t="inlineStr">
         <is>
           <t>Manual NEMET: 8 g/m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>EPOXY VEINS</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D46" t="n">
+        <v>500</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>100</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>20</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Criterio NEMET: vetas ≈20 g/m² (ajustable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>EPOXY-HOJUELA (1 color)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>205</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>100</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>150</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Criterio NEMET: hojuela al voleo ≈150 g/m² (ajustable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>EPOXY-HOJUELA (combinación)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>235</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="n">
+        <v>100</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>150</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Criterio NEMET: hojuela al voleo ≈150 g/m² (ajustable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>EPOXY-GRANO</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>65</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>100</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Criterio NEMET: grano al voleo ≈2.5 kg/m² (ajustable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>EPOXY-GRANO (combinación)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>90</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>100</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Criterio NEMET: grano al voleo ≈2.5 kg/m² (ajustable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>EPOXY-MICA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>470.0000000000001</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>100</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>8</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Manual NEMET: 8 g/m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>EPOXY-MICA (combinado)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>495</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="n">
+        <v>100</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>8</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Manual NEMET: 8 g/m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>EPO-PAINT (A y B)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F53" t="n">
+        <v>100</v>
+      </c>
+      <c r="G53" t="n">
+        <v>50</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Criterio NEMET: ≈0.2 kg/m² por capa</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ARENA SILICA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="n">
+        <v>100</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Criterio NEMET: arena sílica como carga ≈2 kg/m² (ajustable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CÁSCARA DE NARANJA</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>580</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="n">
+        <v>100</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>100</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Criterio NEMET: texturizante al voleo ≈100 g/m² (ajustable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ESTUCO VENECIANO</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>480</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="n">
+        <v>100</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Criterio NEMET: ≈1 L/m² por capa de 1 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>GRANO WALL</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="n">
+        <v>4</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F57" t="n">
+        <v>100</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Criterio NEMET: ≈1.5 L/m² por capa</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>EPOXY CUARZO</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>35</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="n">
+        <v>100</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Criterio NEMET: cuarzo al voleo ≈2.5 kg/m² (ajustable)</t>
         </is>
       </c>
     </row>
@@ -6709,20 +7653,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="31" customWidth="1" min="8" max="8"/>
-    <col width="27" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -6942,6 +7874,7 @@
       <c r="C6" t="n">
         <v>20</v>
       </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>301.45</v>
       </c>
@@ -7053,6 +7986,7 @@
       <c r="C9" t="n">
         <v>20</v>
       </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
         <v>276.35</v>
       </c>
@@ -7202,6 +8136,7 @@
       <c r="C13" t="n">
         <v>20</v>
       </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
         <v>413.8</v>
       </c>
@@ -7351,6 +8286,7 @@
       <c r="C17" t="n">
         <v>17</v>
       </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
         <v>389.43</v>
       </c>
@@ -7500,6 +8436,7 @@
       <c r="C21" t="n">
         <v>24</v>
       </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
         <v>325.58</v>
       </c>
@@ -7649,6 +8586,7 @@
       <c r="C25" t="n">
         <v>19</v>
       </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
         <v>325.58</v>
       </c>
@@ -7722,6 +8660,7 @@
       <c r="C27" t="n">
         <v>60</v>
       </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
         <v>182.7</v>
       </c>
@@ -7795,6 +8734,7 @@
       <c r="C29" t="n">
         <v>60</v>
       </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
         <v>214.5</v>
       </c>
@@ -7868,6 +8808,7 @@
       <c r="C31" t="n">
         <v>60</v>
       </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
         <v>29.34</v>
       </c>
@@ -7886,6 +8827,342 @@
       <c r="J31" t="inlineStr">
         <is>
           <t>+ 60 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>POLIURETANO</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>POLIURETANO (A Y B) TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4.999</v>
+      </c>
+      <c r="E32" t="n">
+        <v>422.11</v>
+      </c>
+      <c r="F32" t="n">
+        <v>460</v>
+      </c>
+      <c r="G32" t="n">
+        <v>37.89</v>
+      </c>
+      <c r="H32" t="n">
+        <v>8.236957</v>
+      </c>
+      <c r="I32" t="n">
+        <v>8.976333</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0 - 4.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>POLIURETANO</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>POLIURETANO (A Y B) TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>9.999000000000001</v>
+      </c>
+      <c r="E33" t="n">
+        <v>395.02</v>
+      </c>
+      <c r="F33" t="n">
+        <v>450</v>
+      </c>
+      <c r="G33" t="n">
+        <v>54.98</v>
+      </c>
+      <c r="H33" t="n">
+        <v>12.217778</v>
+      </c>
+      <c r="I33" t="n">
+        <v>13.918283</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>5 - 9.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>POLIURETANO</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>POLIURETANO (A Y B) TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>10</v>
+      </c>
+      <c r="D34" t="n">
+        <v>19.999</v>
+      </c>
+      <c r="E34" t="n">
+        <v>382.8</v>
+      </c>
+      <c r="F34" t="n">
+        <v>440</v>
+      </c>
+      <c r="G34" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>13</v>
+      </c>
+      <c r="I34" t="n">
+        <v>14.942529</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>10 - 19.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>POLIURETANO</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>POLIURETANO (A Y B) TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>20</v>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>369.09</v>
+      </c>
+      <c r="F35" t="n">
+        <v>430</v>
+      </c>
+      <c r="G35" t="n">
+        <v>60.91</v>
+      </c>
+      <c r="H35" t="n">
+        <v>14.165116</v>
+      </c>
+      <c r="I35" t="n">
+        <v>16.50275</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>+ 20 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ESTUCO VENECIANO</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ESTUCO VENECIANO</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3.999</v>
+      </c>
+      <c r="E36" t="n">
+        <v>400</v>
+      </c>
+      <c r="F36" t="n">
+        <v>480</v>
+      </c>
+      <c r="G36" t="n">
+        <v>80</v>
+      </c>
+      <c r="H36" t="n">
+        <v>16.666667</v>
+      </c>
+      <c r="I36" t="n">
+        <v>20</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1 - 3.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ESTUCO VENECIANO</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ESTUCO VENECIANO</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="n">
+        <v>18.999</v>
+      </c>
+      <c r="E37" t="n">
+        <v>380</v>
+      </c>
+      <c r="F37" t="n">
+        <v>460</v>
+      </c>
+      <c r="G37" t="n">
+        <v>80</v>
+      </c>
+      <c r="H37" t="n">
+        <v>17.391304</v>
+      </c>
+      <c r="I37" t="n">
+        <v>21.052632</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>4 - 18.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ESTUCO VENECIANO</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ESTUCO VENECIANO</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>19</v>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>361</v>
+      </c>
+      <c r="F38" t="n">
+        <v>440</v>
+      </c>
+      <c r="G38" t="n">
+        <v>79</v>
+      </c>
+      <c r="H38" t="n">
+        <v>17.954545</v>
+      </c>
+      <c r="I38" t="n">
+        <v>21.883657</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>+ 19 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>GRANO WALL</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GRANO WALL</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" t="n">
+        <v>18.999</v>
+      </c>
+      <c r="E39" t="n">
+        <v>231.58</v>
+      </c>
+      <c r="F39" t="n">
+        <v>275</v>
+      </c>
+      <c r="G39" t="n">
+        <v>43.42</v>
+      </c>
+      <c r="H39" t="n">
+        <v>15.789091</v>
+      </c>
+      <c r="I39" t="n">
+        <v>18.74946</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>4 - 18.999 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>GRANO WALL</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>GRANO WALL</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>19</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>182.83</v>
+      </c>
+      <c r="F40" t="n">
+        <v>225</v>
+      </c>
+      <c r="G40" t="n">
+        <v>42.17</v>
+      </c>
+      <c r="H40" t="n">
+        <v>18.742222</v>
+      </c>
+      <c r="I40" t="n">
+        <v>23.065142</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>+ 19 kg</t>
         </is>
       </c>
     </row>
